--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -2665,7 +2665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2695,65 +2695,65 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1787536348426</v>
+        <v>1788874820852</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>RELEASED</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D2" t="str">
-        <v>fer</v>
+        <v>Perfecto</v>
       </c>
       <c r="E2" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="F2" t="str">
-        <v>Free Agency</v>
+        <v>BC.Game</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <v>released to market for free</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1785396043745</v>
+        <v>1788874765369</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>PROMOTED</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D3" t="str">
-        <v>boltz</v>
+        <v>kl1m</v>
       </c>
       <c r="E3" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="F3" t="str">
-        <v>Lux Tenebris</v>
+        <v>Envy</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="str">
-        <v>promoted to starter</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1785396042996</v>
+        <v>1787536348426</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="str">
-        <v>BENCHED</v>
+        <v>RELEASED</v>
       </c>
       <c r="D4" t="str">
         <v>fer</v>
@@ -2762,30 +2762,30 @@
         <v>Lux Tenebris</v>
       </c>
       <c r="F4" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v>moved to bench</v>
+        <v>released to market for free</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1785396011356</v>
+        <v>1785396043745</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>FA SIGNING</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D5" t="str">
         <v>boltz</v>
       </c>
       <c r="E5" t="str">
-        <v>Free Agency</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F5" t="str">
         <v>Lux Tenebris</v>
@@ -2794,64 +2794,64 @@
         <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v>joined as Bench</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1783532394458</v>
+        <v>1785396042996</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>FA SIGNING</v>
+        <v>BENCHED</v>
       </c>
       <c r="D6" t="str">
-        <v>diskyb0b</v>
+        <v>fer</v>
       </c>
       <c r="E6" t="str">
-        <v>Free Agency</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F6" t="str">
-        <v>Kappa Bar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="str">
-        <v>joined as Starter</v>
+        <v>moved to bench</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1783532378345</v>
+        <v>1785396011356</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D7" t="str">
-        <v>Gizmy</v>
+        <v>boltz</v>
       </c>
       <c r="E7" t="str">
-        <v>Kappa Bar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F7" t="str">
-        <v>Iluminar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1783532335269</v>
+        <v>1783532394458</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2860,13 +2860,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D8" t="str">
-        <v>hades</v>
+        <v>diskyb0b</v>
       </c>
       <c r="E8" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F8" t="str">
-        <v>Mythic</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>1783532286477</v>
+        <v>1783532378345</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -2886,10 +2886,10 @@
         <v>TRANSFER</v>
       </c>
       <c r="D9" t="str">
-        <v>fl0m</v>
+        <v>Gizmy</v>
       </c>
       <c r="E9" t="str">
-        <v>Mythic</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="F9" t="str">
         <v>Iluminar</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>1783531772696</v>
+        <v>1783532335269</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2912,13 +2912,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D10" t="str">
-        <v>taco</v>
+        <v>hades</v>
       </c>
       <c r="E10" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F10" t="str">
-        <v>Lux Tenebris</v>
+        <v>Mythic</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2929,33 +2929,33 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>1783531758984</v>
+        <v>1783532286477</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D11" t="str">
-        <v>fer</v>
+        <v>fl0m</v>
       </c>
       <c r="E11" t="str">
-        <v>Free Agency</v>
+        <v>Mythic</v>
       </c>
       <c r="F11" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>1783531616692</v>
+        <v>1783531772696</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -2964,7 +2964,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D12" t="str">
-        <v>kyourezz</v>
+        <v>taco</v>
       </c>
       <c r="E12" t="str">
         <v>Free Agency</v>
@@ -2981,118 +2981,170 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>1783531586211</v>
+        <v>1783531758984</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D13" t="str">
-        <v>heroghoxxt</v>
+        <v>fer</v>
       </c>
       <c r="E13" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F13" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G13">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1783531583393</v>
+        <v>1783531616692</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D14" t="str">
-        <v>kilzys</v>
+        <v>kyourezz</v>
       </c>
       <c r="E14" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F14" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G14">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>1783473413103</v>
+        <v>1783531586211</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D15" t="str">
-        <v>taco</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="E15" t="str">
-        <v>Free Agency</v>
+        <v>Iluminar</v>
       </c>
       <c r="F15" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="H15" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>1783473388452</v>
+        <v>1783531583393</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D16" t="str">
-        <v>fer</v>
+        <v>kilzys</v>
       </c>
       <c r="E16" t="str">
-        <v>Free Agency</v>
+        <v>Iluminar</v>
       </c>
       <c r="F16" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G16">
+        <v>50000</v>
+      </c>
+      <c r="H16" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1783473413103</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D17" t="str">
+        <v>taco</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G17">
         <v>0</v>
       </c>
-      <c r="H16" t="str">
+      <c r="H17" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>1783473388452</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D18" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="str">
         <v>joined as Starter</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3119,22 +3171,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1787536347803</v>
+        <v>1788874820765</v>
       </c>
       <c r="B2" t="str">
-        <v>fer</v>
+        <v>Perfecto</v>
       </c>
       <c r="C2" t="str">
-        <v>—</v>
+        <v>BC.Game</v>
       </c>
       <c r="D2" t="str">
-        <v>Lux Tenebris</v>
+        <v>FREE AGENCY</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>✅ RELEASED (FREE)</v>
+        <v>✅ FA SIGNING</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3142,13 +3194,13 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1785396010605</v>
+        <v>1788874765189</v>
       </c>
       <c r="B3" t="str">
-        <v>boltz</v>
+        <v>kl1m</v>
       </c>
       <c r="C3" t="str">
-        <v>Lux Tenebris</v>
+        <v>Envy</v>
       </c>
       <c r="D3" t="str">
         <v>FREE AGENCY</v>
@@ -3163,9 +3215,55 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4">
+        <v>1787536347803</v>
+      </c>
+      <c r="B4" t="str">
+        <v>fer</v>
+      </c>
+      <c r="C4" t="str">
+        <v>—</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v>✅ RELEASED (FREE)</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1785396010605</v>
+      </c>
+      <c r="B5" t="str">
+        <v>boltz</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="D5" t="str">
+        <v>FREE AGENCY</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <v>✅ FA SIGNING</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:M10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,16 +420,28 @@
         <v>scope</v>
       </c>
       <c r="F1" t="str">
+        <v>compRegion</v>
+      </c>
+      <c r="G1" t="str">
         <v>position</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>prizePool</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>wonAmount</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>month</v>
+      </c>
+      <c r="K1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="L1" t="str">
+        <v>awardKey</v>
+      </c>
+      <c r="M1" t="str">
+        <v>note</v>
       </c>
     </row>
     <row r="2">
@@ -449,16 +461,28 @@
         <v>Regional</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>Third</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1500</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>900</v>
       </c>
-      <c r="I2">
-        <v>1</v>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -478,16 +502,28 @@
         <v>Regional</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>Second</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>2000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1200</v>
       </c>
-      <c r="I3">
-        <v>1</v>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -507,16 +543,28 @@
         <v>Regional</v>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
         <v>Winner</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>3000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1800</v>
       </c>
-      <c r="I4">
-        <v>1</v>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -536,16 +584,28 @@
         <v>Regional</v>
       </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>Third</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1500</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>900</v>
       </c>
-      <c r="I5">
-        <v>1</v>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -565,16 +625,28 @@
         <v>Regional</v>
       </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v>Second</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>2000</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1200</v>
       </c>
-      <c r="I6">
-        <v>1</v>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -594,16 +666,28 @@
         <v>Regional</v>
       </c>
       <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
         <v>Winner</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>3000</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1800</v>
       </c>
-      <c r="I7">
-        <v>1</v>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -623,16 +707,28 @@
         <v>Global</v>
       </c>
       <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
         <v>Third</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1790000</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>100000</v>
       </c>
-      <c r="I8">
-        <v>1</v>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -652,16 +748,28 @@
         <v>Global</v>
       </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
         <v>Second</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1790000</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>170000</v>
       </c>
-      <c r="I9">
-        <v>1</v>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -681,28 +789,40 @@
         <v>Global</v>
       </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
         <v>Winner</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1790000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>500000</v>
       </c>
-      <c r="I10">
-        <v>1</v>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:M61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -730,10 +850,19 @@
         <v>scope</v>
       </c>
       <c r="I1" t="str">
+        <v>compRegion</v>
+      </c>
+      <c r="J1" t="str">
         <v>position</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>month</v>
+      </c>
+      <c r="L1" t="str">
+        <v>awardKey</v>
+      </c>
+      <c r="M1" t="str">
+        <v>note</v>
       </c>
     </row>
     <row r="2">
@@ -762,10 +891,19 @@
         <v>Regional</v>
       </c>
       <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
         <v>Winner</v>
       </c>
-      <c r="J2">
-        <v>1</v>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -794,10 +932,19 @@
         <v>Regional</v>
       </c>
       <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>Winner</v>
       </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -826,10 +973,19 @@
         <v>Regional</v>
       </c>
       <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v>Winner</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -858,10 +1014,19 @@
         <v>Regional</v>
       </c>
       <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
         <v>Winner</v>
       </c>
-      <c r="J5">
-        <v>1</v>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -890,10 +1055,19 @@
         <v>Regional</v>
       </c>
       <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v>Winner</v>
       </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -922,10 +1096,19 @@
         <v>Regional</v>
       </c>
       <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
         <v>Third</v>
       </c>
-      <c r="J7">
-        <v>1</v>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -954,10 +1137,19 @@
         <v>Regional</v>
       </c>
       <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v>Third</v>
       </c>
-      <c r="J8">
-        <v>1</v>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -986,10 +1178,19 @@
         <v>Regional</v>
       </c>
       <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v>Third</v>
       </c>
-      <c r="J9">
-        <v>1</v>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1018,10 +1219,19 @@
         <v>Regional</v>
       </c>
       <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v>Third</v>
       </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1050,10 +1260,19 @@
         <v>Regional</v>
       </c>
       <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <v>Third</v>
       </c>
-      <c r="J11">
-        <v>1</v>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1082,10 +1301,19 @@
         <v>Regional</v>
       </c>
       <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <v>Second</v>
       </c>
-      <c r="J12">
-        <v>1</v>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1114,10 +1342,19 @@
         <v>Regional</v>
       </c>
       <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>Second</v>
       </c>
-      <c r="J13">
-        <v>1</v>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1146,10 +1383,19 @@
         <v>Regional</v>
       </c>
       <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v>Second</v>
       </c>
-      <c r="J14">
-        <v>1</v>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1178,10 +1424,19 @@
         <v>Regional</v>
       </c>
       <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v>Second</v>
       </c>
-      <c r="J15">
-        <v>1</v>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1210,10 +1465,19 @@
         <v>Regional</v>
       </c>
       <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>Second</v>
       </c>
-      <c r="J16">
-        <v>1</v>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1242,10 +1506,19 @@
         <v>Regional</v>
       </c>
       <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>Winner</v>
       </c>
-      <c r="J17">
-        <v>1</v>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1274,10 +1547,19 @@
         <v>Regional</v>
       </c>
       <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v>Winner</v>
       </c>
-      <c r="J18">
-        <v>1</v>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1306,10 +1588,19 @@
         <v>Regional</v>
       </c>
       <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>Winner</v>
       </c>
-      <c r="J19">
-        <v>1</v>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1338,10 +1629,19 @@
         <v>Regional</v>
       </c>
       <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v>Winner</v>
       </c>
-      <c r="J20">
-        <v>1</v>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1370,10 +1670,19 @@
         <v>Regional</v>
       </c>
       <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>Winner</v>
       </c>
-      <c r="J21">
-        <v>1</v>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1402,10 +1711,19 @@
         <v>Regional</v>
       </c>
       <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v>Third</v>
       </c>
-      <c r="J22">
-        <v>1</v>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1434,10 +1752,19 @@
         <v>Regional</v>
       </c>
       <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v>Third</v>
       </c>
-      <c r="J23">
-        <v>1</v>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1466,10 +1793,19 @@
         <v>Regional</v>
       </c>
       <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
         <v>Third</v>
       </c>
-      <c r="J24">
-        <v>1</v>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1498,10 +1834,19 @@
         <v>Regional</v>
       </c>
       <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
         <v>Third</v>
       </c>
-      <c r="J25">
-        <v>1</v>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1530,10 +1875,19 @@
         <v>Regional</v>
       </c>
       <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
         <v>Third</v>
       </c>
-      <c r="J26">
-        <v>1</v>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1562,10 +1916,19 @@
         <v>Regional</v>
       </c>
       <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
         <v>Second</v>
       </c>
-      <c r="J27">
-        <v>1</v>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1594,10 +1957,19 @@
         <v>Regional</v>
       </c>
       <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v>Second</v>
       </c>
-      <c r="J28">
-        <v>1</v>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1626,10 +1998,19 @@
         <v>Regional</v>
       </c>
       <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v>Second</v>
       </c>
-      <c r="J29">
-        <v>1</v>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1658,10 +2039,19 @@
         <v>Regional</v>
       </c>
       <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v>Second</v>
       </c>
-      <c r="J30">
-        <v>1</v>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1690,10 +2080,19 @@
         <v>Regional</v>
       </c>
       <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v>Second</v>
       </c>
-      <c r="J31">
-        <v>1</v>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1722,10 +2121,19 @@
         <v>Regional</v>
       </c>
       <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
         <v>Winner</v>
       </c>
-      <c r="J32">
-        <v>1</v>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1754,10 +2162,19 @@
         <v>Regional</v>
       </c>
       <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v>Winner</v>
       </c>
-      <c r="J33">
-        <v>1</v>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1786,10 +2203,19 @@
         <v>Regional</v>
       </c>
       <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
         <v>Winner</v>
       </c>
-      <c r="J34">
-        <v>1</v>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1818,10 +2244,19 @@
         <v>Regional</v>
       </c>
       <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
         <v>Winner</v>
       </c>
-      <c r="J35">
-        <v>1</v>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1850,10 +2285,19 @@
         <v>Regional</v>
       </c>
       <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
         <v>Winner</v>
       </c>
-      <c r="J36">
-        <v>1</v>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1882,10 +2326,19 @@
         <v>Regional</v>
       </c>
       <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v>Second</v>
       </c>
-      <c r="J37">
-        <v>1</v>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1914,10 +2367,19 @@
         <v>Regional</v>
       </c>
       <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v>Second</v>
       </c>
-      <c r="J38">
-        <v>1</v>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1946,10 +2408,19 @@
         <v>Regional</v>
       </c>
       <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v>Winner</v>
       </c>
-      <c r="J39">
-        <v>1</v>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1978,10 +2449,19 @@
         <v>Regional</v>
       </c>
       <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
         <v>Winner</v>
       </c>
-      <c r="J40">
-        <v>1</v>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2010,10 +2490,19 @@
         <v>Regional</v>
       </c>
       <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
         <v>Winner</v>
       </c>
-      <c r="J41">
-        <v>1</v>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2042,10 +2531,19 @@
         <v>Global</v>
       </c>
       <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
         <v>Third</v>
       </c>
-      <c r="J42">
-        <v>1</v>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2074,10 +2572,19 @@
         <v>Global</v>
       </c>
       <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
         <v>Second</v>
       </c>
-      <c r="J43">
-        <v>1</v>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2106,10 +2613,19 @@
         <v>Global</v>
       </c>
       <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
         <v>Second</v>
       </c>
-      <c r="J44">
-        <v>1</v>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2138,10 +2654,19 @@
         <v>Global</v>
       </c>
       <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
         <v>Winner</v>
       </c>
-      <c r="J45">
-        <v>1</v>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2170,10 +2695,19 @@
         <v>Global</v>
       </c>
       <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
         <v>Winner</v>
       </c>
-      <c r="J46">
-        <v>1</v>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2202,10 +2736,19 @@
         <v>Global</v>
       </c>
       <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
         <v>Third</v>
       </c>
-      <c r="J47">
-        <v>1</v>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2234,10 +2777,19 @@
         <v>Global</v>
       </c>
       <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
         <v>Third</v>
       </c>
-      <c r="J48">
-        <v>1</v>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2266,10 +2818,19 @@
         <v>Global</v>
       </c>
       <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
         <v>Third</v>
       </c>
-      <c r="J49">
-        <v>1</v>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2298,10 +2859,19 @@
         <v>Global</v>
       </c>
       <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
         <v>Third</v>
       </c>
-      <c r="J50">
-        <v>1</v>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2330,10 +2900,19 @@
         <v>Global</v>
       </c>
       <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
         <v>Third</v>
       </c>
-      <c r="J51">
-        <v>1</v>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2362,10 +2941,19 @@
         <v>Global</v>
       </c>
       <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
         <v>Second</v>
       </c>
-      <c r="J52">
-        <v>1</v>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -2394,10 +2982,19 @@
         <v>Global</v>
       </c>
       <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
         <v>Second</v>
       </c>
-      <c r="J53">
-        <v>1</v>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2426,10 +3023,19 @@
         <v>Global</v>
       </c>
       <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
         <v>Second</v>
       </c>
-      <c r="J54">
-        <v>1</v>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2458,10 +3064,19 @@
         <v>Global</v>
       </c>
       <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
         <v>Second</v>
       </c>
-      <c r="J55">
-        <v>1</v>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2490,10 +3105,19 @@
         <v>Global</v>
       </c>
       <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
         <v>Second</v>
       </c>
-      <c r="J56">
-        <v>1</v>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2522,10 +3146,19 @@
         <v>Global</v>
       </c>
       <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
         <v>Winner</v>
       </c>
-      <c r="J57">
-        <v>1</v>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -2554,10 +3187,19 @@
         <v>Global</v>
       </c>
       <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
         <v>Winner</v>
       </c>
-      <c r="J58">
-        <v>1</v>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -2586,10 +3228,19 @@
         <v>Global</v>
       </c>
       <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
         <v>Winner</v>
       </c>
-      <c r="J59">
-        <v>1</v>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2618,10 +3269,19 @@
         <v>Global</v>
       </c>
       <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
         <v>Winner</v>
       </c>
-      <c r="J60">
-        <v>1</v>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2650,15 +3310,24 @@
         <v>Global</v>
       </c>
       <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
         <v>Winner</v>
       </c>
-      <c r="J61">
-        <v>1</v>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,31 +446,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1787471977697</v>
+        <v>1789044307262</v>
       </c>
       <c r="B2" t="str">
-        <v>Astana Dragons</v>
+        <v>Nemiga</v>
       </c>
       <c r="C2" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H2">
-        <v>1500</v>
+        <v>1790000</v>
       </c>
       <c r="I2">
-        <v>900</v>
+        <v>45000</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -487,31 +487,31 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1787471970177</v>
+        <v>1789044244253</v>
       </c>
       <c r="B3" t="str">
-        <v>Vox Eminor</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="C3" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H3">
-        <v>2000</v>
+        <v>1790000</v>
       </c>
       <c r="I3">
-        <v>1200</v>
+        <v>45000</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -528,31 +528,31 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1787471959675</v>
+        <v>1789044197304</v>
       </c>
       <c r="B4" t="str">
-        <v>Fnatic</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="C4" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H4">
-        <v>3000</v>
+        <v>1790000</v>
       </c>
       <c r="I4">
-        <v>1800</v>
+        <v>45000</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -569,31 +569,31 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1784854079769</v>
+        <v>1789044064380</v>
       </c>
       <c r="B5" t="str">
-        <v>Entropiq</v>
+        <v>The MongolZ</v>
       </c>
       <c r="C5" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H5">
-        <v>1500</v>
+        <v>1790000</v>
       </c>
       <c r="I5">
-        <v>900</v>
+        <v>45000</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -610,31 +610,31 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>1784854026526</v>
+        <v>1789043946191</v>
       </c>
       <c r="B6" t="str">
-        <v>AMKAL</v>
+        <v>Liquid</v>
       </c>
       <c r="C6" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H6">
-        <v>2000</v>
+        <v>1790000</v>
       </c>
       <c r="I6">
-        <v>1200</v>
+        <v>60000</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -651,13 +651,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1784848026994</v>
+        <v>1787471977697</v>
       </c>
       <c r="B7" t="str">
-        <v>FURIA</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="C7" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -669,13 +669,13 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="H7">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I7">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -692,31 +692,31 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="B8" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="C8" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="H8">
-        <v>1790000</v>
+        <v>2000</v>
       </c>
       <c r="I8">
-        <v>100000</v>
+        <v>1200</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -733,31 +733,31 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>1783531237020</v>
+        <v>1787471959675</v>
       </c>
       <c r="B9" t="str">
-        <v>Vitality</v>
+        <v>Fnatic</v>
       </c>
       <c r="C9" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="H9">
-        <v>1790000</v>
+        <v>3000</v>
       </c>
       <c r="I9">
-        <v>170000</v>
+        <v>1800</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -774,55 +774,260 @@
     </row>
     <row r="10">
       <c r="A10">
+        <v>1784854079769</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="C10" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H10">
+        <v>1500</v>
+      </c>
+      <c r="I10">
+        <v>900</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1784854026526</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="C11" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H11">
+        <v>2000</v>
+      </c>
+      <c r="I11">
+        <v>1200</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1784848026994</v>
+      </c>
+      <c r="B12" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="C12" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H12">
+        <v>3000</v>
+      </c>
+      <c r="I12">
+        <v>1800</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1783531248336</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H13">
+        <v>1790000</v>
+      </c>
+      <c r="I13">
+        <v>100000</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1783531237020</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C14" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H14">
+        <v>1790000</v>
+      </c>
+      <c r="I14">
+        <v>170000</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
         <v>1783531219494</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B15" t="str">
         <v>Iluminar</v>
       </c>
-      <c r="C10" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Global</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
+      <c r="C15" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
         <v>Winner</v>
       </c>
-      <c r="H10">
+      <c r="H15">
         <v>1790000</v>
       </c>
-      <c r="I10">
+      <c r="I15">
         <v>500000</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -866,35 +1071,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1787472254648</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="A2" t="str">
+        <v>1789044307262-sowalio</v>
+      </c>
+      <c r="B2">
+        <v>1789044307262</v>
       </c>
       <c r="C2" t="str">
-        <v>REZ</v>
+        <v>sowalio</v>
       </c>
       <c r="D2" t="str">
-        <v>Astana Dragons</v>
+        <v>Nemiga</v>
       </c>
       <c r="E2" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F2" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -907,35 +1112,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1787472247600</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="A3" t="str">
+        <v>1789044307262-khaN</v>
+      </c>
+      <c r="B3">
+        <v>1789044307262</v>
       </c>
       <c r="C3" t="str">
-        <v>kr1vda</v>
+        <v>khaN</v>
       </c>
       <c r="D3" t="str">
-        <v>Vox Eminor</v>
+        <v>Nemiga</v>
       </c>
       <c r="E3" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F3" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -948,35 +1153,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>1787472243903</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="A4" t="str">
+        <v>1789044307262-riskyb0b</v>
+      </c>
+      <c r="B4">
+        <v>1789044307262</v>
       </c>
       <c r="C4" t="str">
-        <v>fear</v>
+        <v>riskyb0b</v>
       </c>
       <c r="D4" t="str">
-        <v>Fnatic</v>
+        <v>Nemiga</v>
       </c>
       <c r="E4" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F4" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -989,35 +1194,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>1787472232104</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="A5" t="str">
+        <v>1789044307262-1eeR</v>
+      </c>
+      <c r="B5">
+        <v>1789044307262</v>
       </c>
       <c r="C5" t="str">
-        <v>KRIMZ</v>
+        <v>1eeR</v>
       </c>
       <c r="D5" t="str">
-        <v>Fnatic</v>
+        <v>Nemiga</v>
       </c>
       <c r="E5" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F5" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1030,35 +1235,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>1787472226864</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="A6" t="str">
+        <v>1789044307262-Xant3r</v>
+      </c>
+      <c r="B6">
+        <v>1789044307262</v>
       </c>
       <c r="C6" t="str">
-        <v>blameF</v>
+        <v>Xant3r</v>
       </c>
       <c r="D6" t="str">
-        <v>Fnatic</v>
+        <v>Nemiga</v>
       </c>
       <c r="E6" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F6" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1072,34 +1277,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1787471977697-oskar</v>
+        <v>1789044244253-w0nderful</v>
       </c>
       <c r="B7">
-        <v>1787471977697</v>
+        <v>1789044244253</v>
       </c>
       <c r="C7" t="str">
-        <v>oskar</v>
+        <v>w0nderful</v>
       </c>
       <c r="D7" t="str">
-        <v>Astana Dragons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E7" t="str">
         <v>EVENT</v>
       </c>
       <c r="F7" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1113,34 +1318,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1787471977697-PR</v>
+        <v>1789044244253-makazze</v>
       </c>
       <c r="B8">
-        <v>1787471977697</v>
+        <v>1789044244253</v>
       </c>
       <c r="C8" t="str">
-        <v>PR</v>
+        <v>makazze</v>
       </c>
       <c r="D8" t="str">
-        <v>Astana Dragons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E8" t="str">
         <v>EVENT</v>
       </c>
       <c r="F8" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1154,34 +1359,34 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1787471977697-Tauson</v>
+        <v>1789044244253-b1t</v>
       </c>
       <c r="B9">
-        <v>1787471977697</v>
+        <v>1789044244253</v>
       </c>
       <c r="C9" t="str">
-        <v>Tauson</v>
+        <v>b1t</v>
       </c>
       <c r="D9" t="str">
-        <v>Astana Dragons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E9" t="str">
         <v>EVENT</v>
       </c>
       <c r="F9" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1195,34 +1400,34 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1787471977697-ztr</v>
+        <v>1789044244253-iM</v>
       </c>
       <c r="B10">
-        <v>1787471977697</v>
+        <v>1789044244253</v>
       </c>
       <c r="C10" t="str">
-        <v>ztr</v>
+        <v>iM</v>
       </c>
       <c r="D10" t="str">
-        <v>Astana Dragons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E10" t="str">
         <v>EVENT</v>
       </c>
       <c r="F10" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1236,34 +1441,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1787471977697-REZ</v>
+        <v>1789044244253-Aleksib</v>
       </c>
       <c r="B11">
-        <v>1787471977697</v>
+        <v>1789044244253</v>
       </c>
       <c r="C11" t="str">
-        <v>REZ</v>
+        <v>Aleksib</v>
       </c>
       <c r="D11" t="str">
-        <v>Astana Dragons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E11" t="str">
         <v>EVENT</v>
       </c>
       <c r="F11" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1277,34 +1482,34 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1787471970177-OneUn1que</v>
+        <v>1789044197304-Dytor</v>
       </c>
       <c r="B12">
-        <v>1787471970177</v>
+        <v>1789044197304</v>
       </c>
       <c r="C12" t="str">
-        <v>OneUn1que</v>
+        <v>Dytor</v>
       </c>
       <c r="D12" t="str">
-        <v>Vox Eminor</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E12" t="str">
         <v>EVENT</v>
       </c>
       <c r="F12" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1318,34 +1523,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1787471970177-kL1o</v>
+        <v>1789044197304-nbqq</v>
       </c>
       <c r="B13">
-        <v>1787471970177</v>
+        <v>1789044197304</v>
       </c>
       <c r="C13" t="str">
-        <v>kL1o</v>
+        <v>nbqq</v>
       </c>
       <c r="D13" t="str">
-        <v>Vox Eminor</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E13" t="str">
         <v>EVENT</v>
       </c>
       <c r="F13" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1359,34 +1564,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1787471970177-marat2k</v>
+        <v>1789044197304-forsyy</v>
       </c>
       <c r="B14">
-        <v>1787471970177</v>
+        <v>1789044197304</v>
       </c>
       <c r="C14" t="str">
-        <v>marat2k</v>
+        <v>forsyy</v>
       </c>
       <c r="D14" t="str">
-        <v>Vox Eminor</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E14" t="str">
         <v>EVENT</v>
       </c>
       <c r="F14" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1400,34 +1605,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1787471970177-Malkiss</v>
+        <v>1789044197304-ROGA</v>
       </c>
       <c r="B15">
-        <v>1787471970177</v>
+        <v>1789044197304</v>
       </c>
       <c r="C15" t="str">
-        <v>Malkiss</v>
+        <v>ROGA</v>
       </c>
       <c r="D15" t="str">
-        <v>Vox Eminor</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E15" t="str">
         <v>EVENT</v>
       </c>
       <c r="F15" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1441,34 +1646,34 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1787471970177-kr1vda</v>
+        <v>1789044197304-DANK1NG</v>
       </c>
       <c r="B16">
-        <v>1787471970177</v>
+        <v>1789044197304</v>
       </c>
       <c r="C16" t="str">
-        <v>kr1vda</v>
+        <v>DANK1NG</v>
       </c>
       <c r="D16" t="str">
-        <v>Vox Eminor</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E16" t="str">
         <v>EVENT</v>
       </c>
       <c r="F16" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1482,34 +1687,34 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1787471959675-jambo</v>
+        <v>1789044064380-910</v>
       </c>
       <c r="B17">
-        <v>1787471959675</v>
+        <v>1789044064380</v>
       </c>
       <c r="C17" t="str">
-        <v>jambo</v>
+        <v>910</v>
       </c>
       <c r="D17" t="str">
-        <v>Fnatic</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E17" t="str">
         <v>EVENT</v>
       </c>
       <c r="F17" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I17" t="str">
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1523,34 +1728,34 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1787471959675-MATYS</v>
+        <v>1789044064380-mzinho</v>
       </c>
       <c r="B18">
-        <v>1787471959675</v>
+        <v>1789044064380</v>
       </c>
       <c r="C18" t="str">
-        <v>MATYS</v>
+        <v>mzinho</v>
       </c>
       <c r="D18" t="str">
-        <v>Fnatic</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E18" t="str">
         <v>EVENT</v>
       </c>
       <c r="F18" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1564,34 +1769,34 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1787471959675-fear</v>
+        <v>1789044064380-Senzu</v>
       </c>
       <c r="B19">
-        <v>1787471959675</v>
+        <v>1789044064380</v>
       </c>
       <c r="C19" t="str">
-        <v>fear</v>
+        <v>Senzu</v>
       </c>
       <c r="D19" t="str">
-        <v>Fnatic</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E19" t="str">
         <v>EVENT</v>
       </c>
       <c r="F19" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1605,34 +1810,34 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1787471959675-blameF</v>
+        <v>1789044064380-Techno</v>
       </c>
       <c r="B20">
-        <v>1787471959675</v>
+        <v>1789044064380</v>
       </c>
       <c r="C20" t="str">
-        <v>blameF</v>
+        <v>Techno</v>
       </c>
       <c r="D20" t="str">
-        <v>Fnatic</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E20" t="str">
         <v>EVENT</v>
       </c>
       <c r="F20" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -1646,34 +1851,34 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1787471959675-KRIMZ</v>
+        <v>1789044064380-bLitz</v>
       </c>
       <c r="B21">
-        <v>1787471959675</v>
+        <v>1789044064380</v>
       </c>
       <c r="C21" t="str">
-        <v>KRIMZ</v>
+        <v>bLitz</v>
       </c>
       <c r="D21" t="str">
-        <v>Fnatic</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E21" t="str">
         <v>EVENT</v>
       </c>
       <c r="F21" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -1687,34 +1892,34 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1784854079769-Benkai</v>
+        <v>1789043946191-ultimate</v>
       </c>
       <c r="B22">
-        <v>1784854079769</v>
+        <v>1789043946191</v>
       </c>
       <c r="C22" t="str">
-        <v>Benkai</v>
+        <v>ultimate</v>
       </c>
       <c r="D22" t="str">
-        <v>Entropiq</v>
+        <v>Liquid</v>
       </c>
       <c r="E22" t="str">
         <v>EVENT</v>
       </c>
       <c r="F22" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -1728,34 +1933,34 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1784854079769-dea</v>
+        <v>1789043946191-siuhy</v>
       </c>
       <c r="B23">
-        <v>1784854079769</v>
+        <v>1789043946191</v>
       </c>
       <c r="C23" t="str">
-        <v>dea</v>
+        <v>siuhy</v>
       </c>
       <c r="D23" t="str">
-        <v>Entropiq</v>
+        <v>Liquid</v>
       </c>
       <c r="E23" t="str">
         <v>EVENT</v>
       </c>
       <c r="F23" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -1769,34 +1974,34 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1784854079769-shane</v>
+        <v>1789043946191-EliGE</v>
       </c>
       <c r="B24">
-        <v>1784854079769</v>
+        <v>1789043946191</v>
       </c>
       <c r="C24" t="str">
-        <v>shane</v>
+        <v>EliGE</v>
       </c>
       <c r="D24" t="str">
-        <v>Entropiq</v>
+        <v>Liquid</v>
       </c>
       <c r="E24" t="str">
         <v>EVENT</v>
       </c>
       <c r="F24" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -1810,34 +2015,34 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1784854079769-nosraC</v>
+        <v>1789043946191-NertZ</v>
       </c>
       <c r="B25">
-        <v>1784854079769</v>
+        <v>1789043946191</v>
       </c>
       <c r="C25" t="str">
-        <v>nosraC</v>
+        <v>NertZ</v>
       </c>
       <c r="D25" t="str">
-        <v>Entropiq</v>
+        <v>Liquid</v>
       </c>
       <c r="E25" t="str">
         <v>EVENT</v>
       </c>
       <c r="F25" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H25" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -1851,34 +2056,34 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1784854079769-MarKE</v>
+        <v>1789043946191-NAF</v>
       </c>
       <c r="B26">
-        <v>1784854079769</v>
+        <v>1789043946191</v>
       </c>
       <c r="C26" t="str">
-        <v>MarKE</v>
+        <v>NAF</v>
       </c>
       <c r="D26" t="str">
-        <v>Entropiq</v>
+        <v>Liquid</v>
       </c>
       <c r="E26" t="str">
         <v>EVENT</v>
       </c>
       <c r="F26" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -1892,28 +2097,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1784854026526-ivz</v>
+        <v>1783531237020-mezii</v>
       </c>
       <c r="B27">
-        <v>1784854026526</v>
+        <v>1783531237020</v>
       </c>
       <c r="C27" t="str">
-        <v>ivz</v>
+        <v>mezii</v>
       </c>
       <c r="D27" t="str">
-        <v>AMKAL</v>
+        <v>Vitality</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
       </c>
       <c r="F27" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1933,28 +2138,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1784854026526-abizz</v>
+        <v>1783531237020-flameZ</v>
       </c>
       <c r="B28">
-        <v>1784854026526</v>
+        <v>1783531237020</v>
       </c>
       <c r="C28" t="str">
-        <v>abizz</v>
+        <v>flameZ</v>
       </c>
       <c r="D28" t="str">
-        <v>AMKAL</v>
+        <v>Vitality</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
       </c>
       <c r="F28" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1974,28 +2179,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1784854026526-nacho</v>
+        <v>1783531237020-ropz</v>
       </c>
       <c r="B29">
-        <v>1784854026526</v>
+        <v>1783531237020</v>
       </c>
       <c r="C29" t="str">
-        <v>nacho</v>
+        <v>ropz</v>
       </c>
       <c r="D29" t="str">
-        <v>AMKAL</v>
+        <v>Vitality</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
       </c>
       <c r="F29" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -2015,28 +2220,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1784854026526-BK1</v>
+        <v>1783531237020-apEX</v>
       </c>
       <c r="B30">
-        <v>1784854026526</v>
+        <v>1783531237020</v>
       </c>
       <c r="C30" t="str">
-        <v>BK1</v>
+        <v>apEX</v>
       </c>
       <c r="D30" t="str">
-        <v>AMKAL</v>
+        <v>Vitality</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
       </c>
       <c r="F30" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H30" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -2056,28 +2261,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1784854026526-next</v>
+        <v>1783531237020-ZywOo</v>
       </c>
       <c r="B31">
-        <v>1784854026526</v>
+        <v>1783531237020</v>
       </c>
       <c r="C31" t="str">
-        <v>next</v>
+        <v>ZywOo</v>
       </c>
       <c r="D31" t="str">
-        <v>AMKAL</v>
+        <v>Vitality</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
       </c>
       <c r="F31" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H31" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -2097,34 +2302,34 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1783531248336-kyousuke</v>
       </c>
       <c r="B32">
-        <v>1784848026994</v>
+        <v>1783531248336</v>
       </c>
       <c r="C32" t="str">
-        <v>molodoy</v>
+        <v>kyousuke</v>
       </c>
       <c r="D32" t="str">
-        <v>FURIA</v>
+        <v>Falcons</v>
       </c>
       <c r="E32" t="str">
         <v>EVENT</v>
       </c>
       <c r="F32" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H32" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2138,34 +2343,34 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1783531248336-kyxsan</v>
       </c>
       <c r="B33">
-        <v>1784848026994</v>
+        <v>1783531248336</v>
       </c>
       <c r="C33" t="str">
-        <v>KSCERATO</v>
+        <v>kyxsan</v>
       </c>
       <c r="D33" t="str">
-        <v>FURIA</v>
+        <v>Falcons</v>
       </c>
       <c r="E33" t="str">
         <v>EVENT</v>
       </c>
       <c r="F33" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2179,34 +2384,34 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1783531248336-NiKo</v>
       </c>
       <c r="B34">
-        <v>1784848026994</v>
+        <v>1783531248336</v>
       </c>
       <c r="C34" t="str">
-        <v>YEKINDAR</v>
+        <v>NiKo</v>
       </c>
       <c r="D34" t="str">
-        <v>FURIA</v>
+        <v>Falcons</v>
       </c>
       <c r="E34" t="str">
         <v>EVENT</v>
       </c>
       <c r="F34" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2220,34 +2425,34 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1783531248336-TeSeS</v>
       </c>
       <c r="B35">
-        <v>1784848026994</v>
+        <v>1783531248336</v>
       </c>
       <c r="C35" t="str">
-        <v>yuurih</v>
+        <v>TeSeS</v>
       </c>
       <c r="D35" t="str">
-        <v>FURIA</v>
+        <v>Falcons</v>
       </c>
       <c r="E35" t="str">
         <v>EVENT</v>
       </c>
       <c r="F35" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2261,76 +2466,76 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1783531248336-m0NESY</v>
       </c>
       <c r="B36">
-        <v>1784848026994</v>
+        <v>1783531248336</v>
       </c>
       <c r="C36" t="str">
-        <v>FalleN</v>
+        <v>m0NESY</v>
       </c>
       <c r="D36" t="str">
-        <v>FURIA</v>
+        <v>Falcons</v>
       </c>
       <c r="E36" t="str">
         <v>EVENT</v>
       </c>
       <c r="F36" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H36" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>1789043725277-heroghoxxt</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E37" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F37" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v>Winner</v>
       </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>1784847962039</v>
-      </c>
-      <c r="B37" t="str">
-        <v/>
-      </c>
-      <c r="C37" t="str">
-        <v>abizz</v>
-      </c>
-      <c r="D37" t="str">
-        <v>AMKAL</v>
-      </c>
-      <c r="E37" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F37" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Regional</v>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="J37" t="str">
-        <v>Second</v>
-      </c>
       <c r="K37">
         <v>1</v>
       </c>
@@ -2342,35 +2547,35 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>1784847955956</v>
+      <c r="A38" t="str">
+        <v>1789043725277-kilzys</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>next</v>
+        <v>kilzys</v>
       </c>
       <c r="D38" t="str">
-        <v>AMKAL</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E38" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F38" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H38" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -2383,29 +2588,29 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>1784847948890</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="A39" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B39">
+        <v>1783531219494</v>
       </c>
       <c r="C39" t="str">
-        <v>yuurih</v>
+        <v>history</v>
       </c>
       <c r="D39" t="str">
-        <v>FURIA</v>
+        <v>Iluminar</v>
       </c>
       <c r="E39" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F39" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H39" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2424,29 +2629,29 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>1784847943609</v>
-      </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="A40" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B40">
+        <v>1783531219494</v>
       </c>
       <c r="C40" t="str">
-        <v>KSCERATO</v>
+        <v>SpavaQu</v>
       </c>
       <c r="D40" t="str">
-        <v>FURIA</v>
+        <v>Iluminar</v>
       </c>
       <c r="E40" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F40" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H40" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2465,29 +2670,29 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>1784847935905</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="A41" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B41">
+        <v>1783531219494</v>
       </c>
       <c r="C41" t="str">
-        <v>molodoy</v>
+        <v>Pelle</v>
       </c>
       <c r="D41" t="str">
-        <v>FURIA</v>
+        <v>Iluminar</v>
       </c>
       <c r="E41" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F41" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H41" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2507,34 +2712,34 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>1783531290361</v>
+        <v>1787472254648</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>m0NESY</v>
+        <v>REZ</v>
       </c>
       <c r="D42" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E42" t="str">
         <v>VP</v>
       </c>
       <c r="F42" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H42" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -2548,34 +2753,34 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>1783531284605</v>
+        <v>1787472247600</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>ropz</v>
+        <v>kr1vda</v>
       </c>
       <c r="D43" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E43" t="str">
         <v>VP</v>
       </c>
       <c r="F43" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -2589,34 +2794,34 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>1783531278450</v>
+        <v>1787472243903</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>ZywOo</v>
+        <v>fear</v>
       </c>
       <c r="D44" t="str">
-        <v>Vitality</v>
+        <v>Fnatic</v>
       </c>
       <c r="E44" t="str">
-        <v>EVP</v>
+        <v>VP</v>
       </c>
       <c r="F44" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H44" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -2630,28 +2835,28 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>1783531271104</v>
+        <v>1787472232104</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>heroghoxxt</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D45" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E45" t="str">
-        <v>VP</v>
+        <v>EVP</v>
       </c>
       <c r="F45" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H45" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2671,28 +2876,28 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>1783531262507</v>
+        <v>1787472226864</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>kilzys</v>
+        <v>blameF</v>
       </c>
       <c r="D46" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E46" t="str">
         <v>MVP</v>
       </c>
       <c r="F46" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2712,28 +2917,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>1783531248336-kyousuke</v>
+        <v>1787471977697-oskar</v>
       </c>
       <c r="B47">
-        <v>1783531248336</v>
+        <v>1787471977697</v>
       </c>
       <c r="C47" t="str">
-        <v>kyousuke</v>
+        <v>oskar</v>
       </c>
       <c r="D47" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E47" t="str">
         <v>EVENT</v>
       </c>
       <c r="F47" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H47" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2753,28 +2958,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>1783531248336-kyxsan</v>
+        <v>1787471977697-PR</v>
       </c>
       <c r="B48">
-        <v>1783531248336</v>
+        <v>1787471977697</v>
       </c>
       <c r="C48" t="str">
-        <v>kyxsan</v>
+        <v>PR</v>
       </c>
       <c r="D48" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E48" t="str">
         <v>EVENT</v>
       </c>
       <c r="F48" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H48" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2794,28 +2999,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1783531248336-NiKo</v>
+        <v>1787471977697-Tauson</v>
       </c>
       <c r="B49">
-        <v>1783531248336</v>
+        <v>1787471977697</v>
       </c>
       <c r="C49" t="str">
-        <v>NiKo</v>
+        <v>Tauson</v>
       </c>
       <c r="D49" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E49" t="str">
         <v>EVENT</v>
       </c>
       <c r="F49" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H49" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2835,28 +3040,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1783531248336-TeSeS</v>
+        <v>1787471977697-ztr</v>
       </c>
       <c r="B50">
-        <v>1783531248336</v>
+        <v>1787471977697</v>
       </c>
       <c r="C50" t="str">
-        <v>TeSeS</v>
+        <v>ztr</v>
       </c>
       <c r="D50" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E50" t="str">
         <v>EVENT</v>
       </c>
       <c r="F50" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H50" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2876,28 +3081,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1783531248336-m0NESY</v>
+        <v>1787471977697-REZ</v>
       </c>
       <c r="B51">
-        <v>1783531248336</v>
+        <v>1787471977697</v>
       </c>
       <c r="C51" t="str">
-        <v>m0NESY</v>
+        <v>REZ</v>
       </c>
       <c r="D51" t="str">
-        <v>Falcons</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E51" t="str">
         <v>EVENT</v>
       </c>
       <c r="F51" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2917,28 +3122,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1783531237020-mezii</v>
+        <v>1787471970177-OneUn1que</v>
       </c>
       <c r="B52">
-        <v>1783531237020</v>
+        <v>1787471970177</v>
       </c>
       <c r="C52" t="str">
-        <v>mezii</v>
+        <v>OneUn1que</v>
       </c>
       <c r="D52" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E52" t="str">
         <v>EVENT</v>
       </c>
       <c r="F52" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G52">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H52" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2958,28 +3163,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1783531237020-flameZ</v>
+        <v>1787471970177-kL1o</v>
       </c>
       <c r="B53">
-        <v>1783531237020</v>
+        <v>1787471970177</v>
       </c>
       <c r="C53" t="str">
-        <v>flameZ</v>
+        <v>kL1o</v>
       </c>
       <c r="D53" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E53" t="str">
         <v>EVENT</v>
       </c>
       <c r="F53" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H53" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2999,28 +3204,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1783531237020-ropz</v>
+        <v>1787471970177-marat2k</v>
       </c>
       <c r="B54">
-        <v>1783531237020</v>
+        <v>1787471970177</v>
       </c>
       <c r="C54" t="str">
-        <v>ropz</v>
+        <v>marat2k</v>
       </c>
       <c r="D54" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E54" t="str">
         <v>EVENT</v>
       </c>
       <c r="F54" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H54" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -3040,28 +3245,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>1783531237020-apEX</v>
+        <v>1787471970177-Malkiss</v>
       </c>
       <c r="B55">
-        <v>1783531237020</v>
+        <v>1787471970177</v>
       </c>
       <c r="C55" t="str">
-        <v>apEX</v>
+        <v>Malkiss</v>
       </c>
       <c r="D55" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E55" t="str">
         <v>EVENT</v>
       </c>
       <c r="F55" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H55" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -3081,28 +3286,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>1783531237020-ZywOo</v>
+        <v>1787471970177-kr1vda</v>
       </c>
       <c r="B56">
-        <v>1783531237020</v>
+        <v>1787471970177</v>
       </c>
       <c r="C56" t="str">
-        <v>ZywOo</v>
+        <v>kr1vda</v>
       </c>
       <c r="D56" t="str">
-        <v>Vitality</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E56" t="str">
         <v>EVENT</v>
       </c>
       <c r="F56" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H56" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -3122,28 +3327,28 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>1783531219494-history</v>
+        <v>1787471959675-jambo</v>
       </c>
       <c r="B57">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C57" t="str">
-        <v>history</v>
+        <v>jambo</v>
       </c>
       <c r="D57" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E57" t="str">
         <v>EVENT</v>
       </c>
       <c r="F57" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H57" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -3163,28 +3368,28 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1783531219494-heroghoxxt</v>
+        <v>1787471959675-MATYS</v>
       </c>
       <c r="B58">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C58" t="str">
-        <v>heroghoxxt</v>
+        <v>MATYS</v>
       </c>
       <c r="D58" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E58" t="str">
         <v>EVENT</v>
       </c>
       <c r="F58" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H58" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -3204,28 +3409,28 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1783531219494-SpavaQu</v>
+        <v>1787471959675-fear</v>
       </c>
       <c r="B59">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C59" t="str">
-        <v>SpavaQu</v>
+        <v>fear</v>
       </c>
       <c r="D59" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E59" t="str">
         <v>EVENT</v>
       </c>
       <c r="F59" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H59" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -3245,28 +3450,28 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1783531219494-Pelle</v>
+        <v>1787471959675-blameF</v>
       </c>
       <c r="B60">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C60" t="str">
-        <v>Pelle</v>
+        <v>blameF</v>
       </c>
       <c r="D60" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E60" t="str">
         <v>EVENT</v>
       </c>
       <c r="F60" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H60" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -3286,28 +3491,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1783531219494-kilzys</v>
+        <v>1787471959675-KRIMZ</v>
       </c>
       <c r="B61">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C61" t="str">
-        <v>kilzys</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D61" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E61" t="str">
         <v>EVENT</v>
       </c>
       <c r="F61" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H61" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -3325,9 +3530,1034 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>1784854079769-Benkai</v>
+      </c>
+      <c r="B62">
+        <v>1784854079769</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Benkai</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="E62" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F62" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>1784854079769-dea</v>
+      </c>
+      <c r="B63">
+        <v>1784854079769</v>
+      </c>
+      <c r="C63" t="str">
+        <v>dea</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="E63" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F63" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>1784854079769-shane</v>
+      </c>
+      <c r="B64">
+        <v>1784854079769</v>
+      </c>
+      <c r="C64" t="str">
+        <v>shane</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="E64" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F64" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>1784854079769-nosraC</v>
+      </c>
+      <c r="B65">
+        <v>1784854079769</v>
+      </c>
+      <c r="C65" t="str">
+        <v>nosraC</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="E65" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F65" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>1784854079769-MarKE</v>
+      </c>
+      <c r="B66">
+        <v>1784854079769</v>
+      </c>
+      <c r="C66" t="str">
+        <v>MarKE</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="E66" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F66" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>1784854026526-ivz</v>
+      </c>
+      <c r="B67">
+        <v>1784854026526</v>
+      </c>
+      <c r="C67" t="str">
+        <v>ivz</v>
+      </c>
+      <c r="D67" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E67" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F67" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>1784854026526-abizz</v>
+      </c>
+      <c r="B68">
+        <v>1784854026526</v>
+      </c>
+      <c r="C68" t="str">
+        <v>abizz</v>
+      </c>
+      <c r="D68" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E68" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F68" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>1784854026526-nacho</v>
+      </c>
+      <c r="B69">
+        <v>1784854026526</v>
+      </c>
+      <c r="C69" t="str">
+        <v>nacho</v>
+      </c>
+      <c r="D69" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E69" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F69" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>1784854026526-BK1</v>
+      </c>
+      <c r="B70">
+        <v>1784854026526</v>
+      </c>
+      <c r="C70" t="str">
+        <v>BK1</v>
+      </c>
+      <c r="D70" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E70" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F70" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>1784854026526-next</v>
+      </c>
+      <c r="B71">
+        <v>1784854026526</v>
+      </c>
+      <c r="C71" t="str">
+        <v>next</v>
+      </c>
+      <c r="D71" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E71" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F71" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>1784848026994-molodoy</v>
+      </c>
+      <c r="B72">
+        <v>1784848026994</v>
+      </c>
+      <c r="C72" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D72" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E72" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F72" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>1784848026994-KSCERATO</v>
+      </c>
+      <c r="B73">
+        <v>1784848026994</v>
+      </c>
+      <c r="C73" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D73" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E73" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F73" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>1784848026994-YEKINDAR</v>
+      </c>
+      <c r="B74">
+        <v>1784848026994</v>
+      </c>
+      <c r="C74" t="str">
+        <v>YEKINDAR</v>
+      </c>
+      <c r="D74" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E74" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F74" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>1784848026994-yuurih</v>
+      </c>
+      <c r="B75">
+        <v>1784848026994</v>
+      </c>
+      <c r="C75" t="str">
+        <v>yuurih</v>
+      </c>
+      <c r="D75" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E75" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F75" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>1784848026994-FalleN</v>
+      </c>
+      <c r="B76">
+        <v>1784848026994</v>
+      </c>
+      <c r="C76" t="str">
+        <v>FalleN</v>
+      </c>
+      <c r="D76" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E76" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F76" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1784847962039</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v>abizz</v>
+      </c>
+      <c r="D77" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E77" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F77" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>1784847955956</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v>next</v>
+      </c>
+      <c r="D78" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E78" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F78" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>1784847948890</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v>yuurih</v>
+      </c>
+      <c r="D79" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E79" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F79" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>1784847943609</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D80" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E80" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F80" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>1784847935905</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D81" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E81" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F81" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>1783531290361</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E82" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F82" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>1783531284605</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E83" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F83" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G83">
+        <v>5</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>1783531278450</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E84" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F84" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G84">
+        <v>5</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>1783531271104</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E85" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F85" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G85">
+        <v>5</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>1783531262507</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E86" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F86" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M86"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,31 +446,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="B2" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="C2" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G2" t="str">
         <v>Fourth</v>
       </c>
       <c r="H2">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I2">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -487,31 +487,31 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="B3" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="C3" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G3" t="str">
         <v>Fourth</v>
       </c>
       <c r="H3">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I3">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -528,31 +528,31 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="B4" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="C4" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G4" t="str">
         <v>Fourth</v>
       </c>
       <c r="H4">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I4">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -569,31 +569,31 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="B5" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="C5" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G5" t="str">
         <v>Fourth</v>
       </c>
       <c r="H5">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I5">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -610,31 +610,31 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="B6" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="C6" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G6" t="str">
         <v>Fourth</v>
       </c>
       <c r="H6">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I6">
-        <v>60000</v>
+        <v>700</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -651,13 +651,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1787471977697</v>
+        <v>1789045299584</v>
       </c>
       <c r="B7" t="str">
-        <v>Astana Dragons</v>
+        <v>Mythic</v>
       </c>
       <c r="C7" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -666,16 +666,16 @@
         <v>Regional</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G7" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H7">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="I7">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -692,13 +692,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1787471970177</v>
+        <v>1789045274106</v>
       </c>
       <c r="B8" t="str">
-        <v>Vox Eminor</v>
+        <v>paiN Academy</v>
       </c>
       <c r="C8" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -707,16 +707,16 @@
         <v>Regional</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G8" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H8">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>1787471959675</v>
+        <v>1789045224902</v>
       </c>
       <c r="B9" t="str">
-        <v>Fnatic</v>
+        <v>Legacy</v>
       </c>
       <c r="C9" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -748,16 +748,16 @@
         <v>Regional</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G9" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H9">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="I9">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -774,10 +774,10 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>1784854079769</v>
+        <v>1789045150461</v>
       </c>
       <c r="B10" t="str">
-        <v>Entropiq</v>
+        <v>Into the Beach</v>
       </c>
       <c r="C10" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -789,16 +789,16 @@
         <v>Regional</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G10" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H10">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="I10">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>1784854026526</v>
+        <v>1789045118610</v>
       </c>
       <c r="B11" t="str">
-        <v>AMKAL</v>
+        <v>Take Flyte</v>
       </c>
       <c r="C11" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -830,16 +830,16 @@
         <v>Regional</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G11" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H11">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I11">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -856,31 +856,31 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>1784848026994</v>
+        <v>1789044307262</v>
       </c>
       <c r="B12" t="str">
-        <v>FURIA</v>
+        <v>Nemiga</v>
       </c>
       <c r="C12" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H12">
-        <v>3000</v>
+        <v>1790000</v>
       </c>
       <c r="I12">
-        <v>1800</v>
+        <v>45000</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>1783531248336</v>
+        <v>1789044244253</v>
       </c>
       <c r="B13" t="str">
-        <v>Falcons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="C13" t="str">
         <v>DreamHack Winter 2026</v>
@@ -915,13 +915,13 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H13">
         <v>1790000</v>
       </c>
       <c r="I13">
-        <v>100000</v>
+        <v>45000</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -938,10 +938,10 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>1783531237020</v>
+        <v>1789044197304</v>
       </c>
       <c r="B14" t="str">
-        <v>Vitality</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="C14" t="str">
         <v>DreamHack Winter 2026</v>
@@ -956,13 +956,13 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H14">
         <v>1790000</v>
       </c>
       <c r="I14">
-        <v>170000</v>
+        <v>45000</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -979,10 +979,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>1783531219494</v>
+        <v>1789044064380</v>
       </c>
       <c r="B15" t="str">
-        <v>Iluminar</v>
+        <v>The MongolZ</v>
       </c>
       <c r="C15" t="str">
         <v>DreamHack Winter 2026</v>
@@ -997,37 +997,447 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H15">
         <v>1790000</v>
       </c>
       <c r="I15">
+        <v>45000</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>1789043946191</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="H16">
+        <v>1790000</v>
+      </c>
+      <c r="I16">
+        <v>60000</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1787471977697</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Astana Dragons</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H17">
+        <v>10000</v>
+      </c>
+      <c r="I17">
+        <v>1500</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>1787471970177</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Vox Eminor</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H18">
+        <v>10000</v>
+      </c>
+      <c r="I18">
+        <v>2000</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>1787471959675</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H19">
+        <v>10000</v>
+      </c>
+      <c r="I19">
+        <v>3000</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>1784854079769</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="C20" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F20" t="str">
+        <v>America</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H20">
+        <v>10000</v>
+      </c>
+      <c r="I20">
+        <v>1500</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1784854026526</v>
+      </c>
+      <c r="B21" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="C21" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F21" t="str">
+        <v>America</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H21">
+        <v>10000</v>
+      </c>
+      <c r="I21">
+        <v>2000</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>1784848026994</v>
+      </c>
+      <c r="B22" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F22" t="str">
+        <v>America</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H22">
+        <v>10000</v>
+      </c>
+      <c r="I22">
+        <v>3000</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>1783531248336</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="C23" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H23">
+        <v>1790000</v>
+      </c>
+      <c r="I23">
+        <v>100000</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>1783531237020</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C24" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H24">
+        <v>1790000</v>
+      </c>
+      <c r="I24">
+        <v>170000</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1783531219494</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="C25" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H25">
+        <v>1790000</v>
+      </c>
+      <c r="I25">
         <v>500000</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M135"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1072,31 +1482,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1789044307262-sowalio</v>
+        <v>1789045649533-ykis</v>
       </c>
       <c r="B2">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="C2" t="str">
-        <v>sowalio</v>
+        <v>ykis</v>
       </c>
       <c r="D2" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E2" t="str">
         <v>EVENT</v>
       </c>
       <c r="F2" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J2" t="str">
         <v>Fourth</v>
@@ -1113,31 +1523,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1789044307262-khaN</v>
+        <v>1789045649533-japE</v>
       </c>
       <c r="B3">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="C3" t="str">
-        <v>khaN</v>
+        <v>japE</v>
       </c>
       <c r="D3" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E3" t="str">
         <v>EVENT</v>
       </c>
       <c r="F3" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J3" t="str">
         <v>Fourth</v>
@@ -1154,31 +1564,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1789044307262-riskyb0b</v>
+        <v>1789045649533-Welho</v>
       </c>
       <c r="B4">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="C4" t="str">
-        <v>riskyb0b</v>
+        <v>Welho</v>
       </c>
       <c r="D4" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E4" t="str">
         <v>EVENT</v>
       </c>
       <c r="F4" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J4" t="str">
         <v>Fourth</v>
@@ -1195,31 +1605,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1789044307262-1eeR</v>
+        <v>1789045649533-oopee</v>
       </c>
       <c r="B5">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="C5" t="str">
-        <v>1eeR</v>
+        <v>oopee</v>
       </c>
       <c r="D5" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E5" t="str">
         <v>EVENT</v>
       </c>
       <c r="F5" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J5" t="str">
         <v>Fourth</v>
@@ -1236,31 +1646,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1789044307262-Xant3r</v>
+        <v>1789045649533-arvid</v>
       </c>
       <c r="B6">
-        <v>1789044307262</v>
+        <v>1789045649533</v>
       </c>
       <c r="C6" t="str">
-        <v>Xant3r</v>
+        <v>arvid</v>
       </c>
       <c r="D6" t="str">
-        <v>Nemiga</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E6" t="str">
         <v>EVENT</v>
       </c>
       <c r="F6" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J6" t="str">
         <v>Fourth</v>
@@ -1277,31 +1687,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1789044244253-w0nderful</v>
+        <v>1789045609684-2high</v>
       </c>
       <c r="B7">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="C7" t="str">
-        <v>w0nderful</v>
+        <v>2high</v>
       </c>
       <c r="D7" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E7" t="str">
         <v>EVENT</v>
       </c>
       <c r="F7" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J7" t="str">
         <v>Fourth</v>
@@ -1318,31 +1728,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1789044244253-makazze</v>
+        <v>1789045609684-jL</v>
       </c>
       <c r="B8">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="C8" t="str">
-        <v>makazze</v>
+        <v>jL</v>
       </c>
       <c r="D8" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E8" t="str">
         <v>EVENT</v>
       </c>
       <c r="F8" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J8" t="str">
         <v>Fourth</v>
@@ -1359,31 +1769,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1789044244253-b1t</v>
+        <v>1789045609684-aliStair</v>
       </c>
       <c r="B9">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="C9" t="str">
-        <v>b1t</v>
+        <v>aliStair</v>
       </c>
       <c r="D9" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E9" t="str">
         <v>EVENT</v>
       </c>
       <c r="F9" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J9" t="str">
         <v>Fourth</v>
@@ -1400,31 +1810,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1789044244253-iM</v>
+        <v>1789045609684-gla1ve</v>
       </c>
       <c r="B10">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="C10" t="str">
-        <v>iM</v>
+        <v>gla1ve</v>
       </c>
       <c r="D10" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E10" t="str">
         <v>EVENT</v>
       </c>
       <c r="F10" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H10" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J10" t="str">
         <v>Fourth</v>
@@ -1441,31 +1851,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1789044244253-Aleksib</v>
+        <v>1789045609684-discoStar</v>
       </c>
       <c r="B11">
-        <v>1789044244253</v>
+        <v>1789045609684</v>
       </c>
       <c r="C11" t="str">
-        <v>Aleksib</v>
+        <v>discoStar</v>
       </c>
       <c r="D11" t="str">
-        <v>Natus Vincere</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E11" t="str">
         <v>EVENT</v>
       </c>
       <c r="F11" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J11" t="str">
         <v>Fourth</v>
@@ -1482,31 +1892,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1789044197304-Dytor</v>
+        <v>1789045581410-forkyz</v>
       </c>
       <c r="B12">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="C12" t="str">
-        <v>Dytor</v>
+        <v>forkyz</v>
       </c>
       <c r="D12" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E12" t="str">
         <v>EVENT</v>
       </c>
       <c r="F12" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J12" t="str">
         <v>Fourth</v>
@@ -1523,31 +1933,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1789044197304-nbqq</v>
+        <v>1789045581410-Pumpkin66</v>
       </c>
       <c r="B13">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="C13" t="str">
-        <v>nbqq</v>
+        <v>Pumpkin66</v>
       </c>
       <c r="D13" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E13" t="str">
         <v>EVENT</v>
       </c>
       <c r="F13" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J13" t="str">
         <v>Fourth</v>
@@ -1564,31 +1974,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1789044197304-forsyy</v>
+        <v>1789045581410-def1zer</v>
       </c>
       <c r="B14">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="C14" t="str">
-        <v>forsyy</v>
+        <v>def1zer</v>
       </c>
       <c r="D14" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E14" t="str">
         <v>EVENT</v>
       </c>
       <c r="F14" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J14" t="str">
         <v>Fourth</v>
@@ -1605,31 +2015,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1789044197304-ROGA</v>
+        <v>1789045581410-buster</v>
       </c>
       <c r="B15">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="C15" t="str">
-        <v>ROGA</v>
+        <v>buster</v>
       </c>
       <c r="D15" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E15" t="str">
         <v>EVENT</v>
       </c>
       <c r="F15" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J15" t="str">
         <v>Fourth</v>
@@ -1646,31 +2056,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1789044197304-DANK1NG</v>
+        <v>1789045581410-neaLaN</v>
       </c>
       <c r="B16">
-        <v>1789044197304</v>
+        <v>1789045581410</v>
       </c>
       <c r="C16" t="str">
-        <v>DANK1NG</v>
+        <v>neaLaN</v>
       </c>
       <c r="D16" t="str">
-        <v>Copenhagen Flames</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E16" t="str">
         <v>EVENT</v>
       </c>
       <c r="F16" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J16" t="str">
         <v>Fourth</v>
@@ -1687,31 +2097,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1789044064380-910</v>
+        <v>1789045560109-cerber</v>
       </c>
       <c r="B17">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="C17" t="str">
-        <v>910</v>
+        <v>cerber</v>
       </c>
       <c r="D17" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E17" t="str">
         <v>EVENT</v>
       </c>
       <c r="F17" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J17" t="str">
         <v>Fourth</v>
@@ -1728,31 +2138,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1789044064380-mzinho</v>
+        <v>1789045560109-SinK</v>
       </c>
       <c r="B18">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="C18" t="str">
-        <v>mzinho</v>
+        <v>SinK</v>
       </c>
       <c r="D18" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E18" t="str">
         <v>EVENT</v>
       </c>
       <c r="F18" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J18" t="str">
         <v>Fourth</v>
@@ -1769,31 +2179,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1789044064380-Senzu</v>
+        <v>1789045560109-qx</v>
       </c>
       <c r="B19">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="C19" t="str">
-        <v>Senzu</v>
+        <v>qx</v>
       </c>
       <c r="D19" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E19" t="str">
         <v>EVENT</v>
       </c>
       <c r="F19" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J19" t="str">
         <v>Fourth</v>
@@ -1810,31 +2220,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1789044064380-Techno</v>
+        <v>1789045560109-Griller</v>
       </c>
       <c r="B20">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="C20" t="str">
-        <v>Techno</v>
+        <v>Griller</v>
       </c>
       <c r="D20" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E20" t="str">
         <v>EVENT</v>
       </c>
       <c r="F20" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J20" t="str">
         <v>Fourth</v>
@@ -1851,31 +2261,31 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1789044064380-bLitz</v>
+        <v>1789045560109-AclioN</v>
       </c>
       <c r="B21">
-        <v>1789044064380</v>
+        <v>1789045560109</v>
       </c>
       <c r="C21" t="str">
-        <v>bLitz</v>
+        <v>AclioN</v>
       </c>
       <c r="D21" t="str">
-        <v>The MongolZ</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E21" t="str">
         <v>EVENT</v>
       </c>
       <c r="F21" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J21" t="str">
         <v>Fourth</v>
@@ -1892,31 +2302,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1789043946191-ultimate</v>
+        <v>1789045530768-Matheos</v>
       </c>
       <c r="B22">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="C22" t="str">
-        <v>ultimate</v>
+        <v>Matheos</v>
       </c>
       <c r="D22" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E22" t="str">
         <v>EVENT</v>
       </c>
       <c r="F22" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J22" t="str">
         <v>Fourth</v>
@@ -1933,31 +2343,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1789043946191-siuhy</v>
+        <v>1789045530768-Jorko</v>
       </c>
       <c r="B23">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="C23" t="str">
-        <v>siuhy</v>
+        <v>Jorko</v>
       </c>
       <c r="D23" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E23" t="str">
         <v>EVENT</v>
       </c>
       <c r="F23" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J23" t="str">
         <v>Fourth</v>
@@ -1974,31 +2384,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1789043946191-EliGE</v>
+        <v>1789045530768-Tapewaare</v>
       </c>
       <c r="B24">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="C24" t="str">
-        <v>EliGE</v>
+        <v>Tapewaare</v>
       </c>
       <c r="D24" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E24" t="str">
         <v>EVENT</v>
       </c>
       <c r="F24" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J24" t="str">
         <v>Fourth</v>
@@ -2015,31 +2425,31 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1789043946191-NertZ</v>
+        <v>1789045530768-b1elany</v>
       </c>
       <c r="B25">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="C25" t="str">
-        <v>NertZ</v>
+        <v>b1elany</v>
       </c>
       <c r="D25" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E25" t="str">
         <v>EVENT</v>
       </c>
       <c r="F25" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J25" t="str">
         <v>Fourth</v>
@@ -2056,31 +2466,31 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1789043946191-NAF</v>
+        <v>1789045530768-n1Xen</v>
       </c>
       <c r="B26">
-        <v>1789043946191</v>
+        <v>1789045530768</v>
       </c>
       <c r="C26" t="str">
-        <v>NAF</v>
+        <v>n1Xen</v>
       </c>
       <c r="D26" t="str">
-        <v>Liquid</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E26" t="str">
         <v>EVENT</v>
       </c>
       <c r="F26" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J26" t="str">
         <v>Fourth</v>
@@ -2097,34 +2507,34 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1783531237020-mezii</v>
+        <v>1787471977697-oskar</v>
       </c>
       <c r="B27">
-        <v>1783531237020</v>
+        <v>1787471977697</v>
       </c>
       <c r="C27" t="str">
-        <v>mezii</v>
+        <v>oskar</v>
       </c>
       <c r="D27" t="str">
-        <v>Vitality</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
       </c>
       <c r="F27" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J27" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2138,34 +2548,34 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1783531237020-flameZ</v>
+        <v>1787471977697-PR</v>
       </c>
       <c r="B28">
-        <v>1783531237020</v>
+        <v>1787471977697</v>
       </c>
       <c r="C28" t="str">
-        <v>flameZ</v>
+        <v>PR</v>
       </c>
       <c r="D28" t="str">
-        <v>Vitality</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
       </c>
       <c r="F28" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J28" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2179,34 +2589,34 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1783531237020-ropz</v>
+        <v>1787471977697-Tauson</v>
       </c>
       <c r="B29">
-        <v>1783531237020</v>
+        <v>1787471977697</v>
       </c>
       <c r="C29" t="str">
-        <v>ropz</v>
+        <v>Tauson</v>
       </c>
       <c r="D29" t="str">
-        <v>Vitality</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
       </c>
       <c r="F29" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J29" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2220,34 +2630,34 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1783531237020-apEX</v>
+        <v>1787471977697-ztr</v>
       </c>
       <c r="B30">
-        <v>1783531237020</v>
+        <v>1787471977697</v>
       </c>
       <c r="C30" t="str">
-        <v>apEX</v>
+        <v>ztr</v>
       </c>
       <c r="D30" t="str">
-        <v>Vitality</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
       </c>
       <c r="F30" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J30" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2261,34 +2671,34 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1783531237020-ZywOo</v>
+        <v>1787471977697-REZ</v>
       </c>
       <c r="B31">
-        <v>1783531237020</v>
+        <v>1787471977697</v>
       </c>
       <c r="C31" t="str">
-        <v>ZywOo</v>
+        <v>REZ</v>
       </c>
       <c r="D31" t="str">
-        <v>Vitality</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
       </c>
       <c r="F31" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J31" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2302,34 +2712,34 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1783531248336-kyousuke</v>
+        <v>1787471970177-OneUn1que</v>
       </c>
       <c r="B32">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="C32" t="str">
-        <v>kyousuke</v>
+        <v>OneUn1que</v>
       </c>
       <c r="D32" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E32" t="str">
         <v>EVENT</v>
       </c>
       <c r="F32" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J32" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2343,34 +2753,34 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1783531248336-kyxsan</v>
+        <v>1787471970177-kL1o</v>
       </c>
       <c r="B33">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="C33" t="str">
-        <v>kyxsan</v>
+        <v>kL1o</v>
       </c>
       <c r="D33" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E33" t="str">
         <v>EVENT</v>
       </c>
       <c r="F33" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H33" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J33" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2384,34 +2794,34 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1783531248336-NiKo</v>
+        <v>1787471970177-marat2k</v>
       </c>
       <c r="B34">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="C34" t="str">
-        <v>NiKo</v>
+        <v>marat2k</v>
       </c>
       <c r="D34" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E34" t="str">
         <v>EVENT</v>
       </c>
       <c r="F34" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J34" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2425,34 +2835,34 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1783531248336-TeSeS</v>
+        <v>1787471970177-Malkiss</v>
       </c>
       <c r="B35">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="C35" t="str">
-        <v>TeSeS</v>
+        <v>Malkiss</v>
       </c>
       <c r="D35" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E35" t="str">
         <v>EVENT</v>
       </c>
       <c r="F35" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H35" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J35" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2466,34 +2876,34 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1783531248336-m0NESY</v>
+        <v>1787471970177-kr1vda</v>
       </c>
       <c r="B36">
-        <v>1783531248336</v>
+        <v>1787471970177</v>
       </c>
       <c r="C36" t="str">
-        <v>m0NESY</v>
+        <v>kr1vda</v>
       </c>
       <c r="D36" t="str">
-        <v>Falcons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E36" t="str">
         <v>EVENT</v>
       </c>
       <c r="F36" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J36" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2507,31 +2917,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1789043725277-heroghoxxt</v>
-      </c>
-      <c r="B37" t="str">
-        <v/>
+        <v>1787471959675-jambo</v>
+      </c>
+      <c r="B37">
+        <v>1787471959675</v>
       </c>
       <c r="C37" t="str">
-        <v>heroghoxxt</v>
+        <v>jambo</v>
       </c>
       <c r="D37" t="str">
-        <v>Lux Tenebris</v>
+        <v>Fnatic</v>
       </c>
       <c r="E37" t="str">
         <v>EVENT</v>
       </c>
       <c r="F37" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J37" t="str">
         <v>Winner</v>
@@ -2548,31 +2958,31 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1789043725277-kilzys</v>
-      </c>
-      <c r="B38" t="str">
-        <v/>
+        <v>1787471959675-fear</v>
+      </c>
+      <c r="B38">
+        <v>1787471959675</v>
       </c>
       <c r="C38" t="str">
-        <v>kilzys</v>
+        <v>fear</v>
       </c>
       <c r="D38" t="str">
-        <v>Lux Tenebris</v>
+        <v>Fnatic</v>
       </c>
       <c r="E38" t="str">
         <v>EVENT</v>
       </c>
       <c r="F38" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J38" t="str">
         <v>Winner</v>
@@ -2589,31 +2999,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1783531219494-history</v>
+        <v>1787471959675-blameF</v>
       </c>
       <c r="B39">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C39" t="str">
-        <v>history</v>
+        <v>blameF</v>
       </c>
       <c r="D39" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E39" t="str">
         <v>EVENT</v>
       </c>
       <c r="F39" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H39" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J39" t="str">
         <v>Winner</v>
@@ -2630,31 +3040,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1783531219494-SpavaQu</v>
+        <v>1787471959675-KRIMZ</v>
       </c>
       <c r="B40">
-        <v>1783531219494</v>
+        <v>1787471959675</v>
       </c>
       <c r="C40" t="str">
-        <v>SpavaQu</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D40" t="str">
-        <v>Iluminar</v>
+        <v>Fnatic</v>
       </c>
       <c r="E40" t="str">
         <v>EVENT</v>
       </c>
       <c r="F40" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H40" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J40" t="str">
         <v>Winner</v>
@@ -2671,34 +3081,34 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1783531219494-Pelle</v>
+        <v>1789045299584-hades</v>
       </c>
       <c r="B41">
-        <v>1783531219494</v>
+        <v>1789045299584</v>
       </c>
       <c r="C41" t="str">
-        <v>Pelle</v>
+        <v>hades</v>
       </c>
       <c r="D41" t="str">
-        <v>Iluminar</v>
+        <v>Mythic</v>
       </c>
       <c r="E41" t="str">
         <v>EVENT</v>
       </c>
       <c r="F41" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H41" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J41" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -2711,23 +3121,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>1787472254648</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="A42" t="str">
+        <v>1789045299584-PwnAlone</v>
+      </c>
+      <c r="B42">
+        <v>1789045299584</v>
       </c>
       <c r="C42" t="str">
-        <v>REZ</v>
+        <v>PwnAlone</v>
       </c>
       <c r="D42" t="str">
-        <v>Astana Dragons</v>
+        <v>Mythic</v>
       </c>
       <c r="E42" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F42" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2736,10 +3146,10 @@
         <v>Regional</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J42" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -2752,23 +3162,23 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>1787472247600</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="A43" t="str">
+        <v>1789045299584-Trucklover86</v>
+      </c>
+      <c r="B43">
+        <v>1789045299584</v>
       </c>
       <c r="C43" t="str">
-        <v>kr1vda</v>
+        <v>Trucklover86</v>
       </c>
       <c r="D43" t="str">
-        <v>Vox Eminor</v>
+        <v>Mythic</v>
       </c>
       <c r="E43" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F43" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2777,10 +3187,10 @@
         <v>Regional</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J43" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -2793,23 +3203,23 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>1787472243903</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="A44" t="str">
+        <v>1789045299584-hyza</v>
+      </c>
+      <c r="B44">
+        <v>1789045299584</v>
       </c>
       <c r="C44" t="str">
-        <v>fear</v>
+        <v>hyza</v>
       </c>
       <c r="D44" t="str">
-        <v>Fnatic</v>
+        <v>Mythic</v>
       </c>
       <c r="E44" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F44" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2818,10 +3228,10 @@
         <v>Regional</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J44" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -2834,23 +3244,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>1787472232104</v>
-      </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="A45" t="str">
+        <v>1789045299584-Cooper</v>
+      </c>
+      <c r="B45">
+        <v>1789045299584</v>
       </c>
       <c r="C45" t="str">
-        <v>KRIMZ</v>
+        <v>Cooper</v>
       </c>
       <c r="D45" t="str">
-        <v>Fnatic</v>
+        <v>Mythic</v>
       </c>
       <c r="E45" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F45" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2859,10 +3269,10 @@
         <v>Regional</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J45" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -2875,23 +3285,23 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>1787472226864</v>
-      </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="A46" t="str">
+        <v>1789045274106-blaze</v>
+      </c>
+      <c r="B46">
+        <v>1789045274106</v>
       </c>
       <c r="C46" t="str">
-        <v>blameF</v>
+        <v>blaze</v>
       </c>
       <c r="D46" t="str">
-        <v>Fnatic</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E46" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F46" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2900,10 +3310,10 @@
         <v>Regional</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J46" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -2917,22 +3327,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>1787471977697-oskar</v>
+        <v>1789045274106-h0t</v>
       </c>
       <c r="B47">
-        <v>1787471977697</v>
+        <v>1789045274106</v>
       </c>
       <c r="C47" t="str">
-        <v>oskar</v>
+        <v>h0t</v>
       </c>
       <c r="D47" t="str">
-        <v>Astana Dragons</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E47" t="str">
         <v>EVENT</v>
       </c>
       <c r="F47" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2941,10 +3351,10 @@
         <v>Regional</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J47" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -2958,22 +3368,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>1787471977697-PR</v>
+        <v>1789045274106-bsd</v>
       </c>
       <c r="B48">
-        <v>1787471977697</v>
+        <v>1789045274106</v>
       </c>
       <c r="C48" t="str">
-        <v>PR</v>
+        <v>bsd</v>
       </c>
       <c r="D48" t="str">
-        <v>Astana Dragons</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E48" t="str">
         <v>EVENT</v>
       </c>
       <c r="F48" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2982,10 +3392,10 @@
         <v>Regional</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J48" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -2999,22 +3409,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1787471977697-Tauson</v>
+        <v>1789045274106-b4rtiN</v>
       </c>
       <c r="B49">
-        <v>1787471977697</v>
+        <v>1789045274106</v>
       </c>
       <c r="C49" t="str">
-        <v>Tauson</v>
+        <v>b4rtiN</v>
       </c>
       <c r="D49" t="str">
-        <v>Astana Dragons</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E49" t="str">
         <v>EVENT</v>
       </c>
       <c r="F49" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3023,10 +3433,10 @@
         <v>Regional</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J49" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -3040,22 +3450,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1787471977697-ztr</v>
+        <v>1789045274106-NEKIZ</v>
       </c>
       <c r="B50">
-        <v>1787471977697</v>
+        <v>1789045274106</v>
       </c>
       <c r="C50" t="str">
-        <v>ztr</v>
+        <v>NEKIZ</v>
       </c>
       <c r="D50" t="str">
-        <v>Astana Dragons</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E50" t="str">
         <v>EVENT</v>
       </c>
       <c r="F50" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3064,10 +3474,10 @@
         <v>Regional</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J50" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -3081,22 +3491,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1787471977697-REZ</v>
+        <v>1789045224902-saadzin</v>
       </c>
       <c r="B51">
-        <v>1787471977697</v>
+        <v>1789045224902</v>
       </c>
       <c r="C51" t="str">
-        <v>REZ</v>
+        <v>saadzin</v>
       </c>
       <c r="D51" t="str">
-        <v>Astana Dragons</v>
+        <v>Legacy</v>
       </c>
       <c r="E51" t="str">
         <v>EVENT</v>
       </c>
       <c r="F51" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -3105,10 +3515,10 @@
         <v>Regional</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J51" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -3122,22 +3532,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1787471970177-OneUn1que</v>
+        <v>1789045224902-lux</v>
       </c>
       <c r="B52">
-        <v>1787471970177</v>
+        <v>1789045224902</v>
       </c>
       <c r="C52" t="str">
-        <v>OneUn1que</v>
+        <v>lux</v>
       </c>
       <c r="D52" t="str">
-        <v>Vox Eminor</v>
+        <v>Legacy</v>
       </c>
       <c r="E52" t="str">
         <v>EVENT</v>
       </c>
       <c r="F52" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -3146,10 +3556,10 @@
         <v>Regional</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J52" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3163,22 +3573,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1787471970177-kL1o</v>
+        <v>1789045224902-n1ssim</v>
       </c>
       <c r="B53">
-        <v>1787471970177</v>
+        <v>1789045224902</v>
       </c>
       <c r="C53" t="str">
-        <v>kL1o</v>
+        <v>n1ssim</v>
       </c>
       <c r="D53" t="str">
-        <v>Vox Eminor</v>
+        <v>Legacy</v>
       </c>
       <c r="E53" t="str">
         <v>EVENT</v>
       </c>
       <c r="F53" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3187,10 +3597,10 @@
         <v>Regional</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J53" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K53">
         <v>1</v>
@@ -3204,22 +3614,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1787471970177-marat2k</v>
+        <v>1789045224902-latto</v>
       </c>
       <c r="B54">
-        <v>1787471970177</v>
+        <v>1789045224902</v>
       </c>
       <c r="C54" t="str">
-        <v>marat2k</v>
+        <v>latto</v>
       </c>
       <c r="D54" t="str">
-        <v>Vox Eminor</v>
+        <v>Legacy</v>
       </c>
       <c r="E54" t="str">
         <v>EVENT</v>
       </c>
       <c r="F54" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3228,10 +3638,10 @@
         <v>Regional</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J54" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -3245,22 +3655,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>1787471970177-Malkiss</v>
+        <v>1789045224902-dumau</v>
       </c>
       <c r="B55">
-        <v>1787471970177</v>
+        <v>1789045224902</v>
       </c>
       <c r="C55" t="str">
-        <v>Malkiss</v>
+        <v>dumau</v>
       </c>
       <c r="D55" t="str">
-        <v>Vox Eminor</v>
+        <v>Legacy</v>
       </c>
       <c r="E55" t="str">
         <v>EVENT</v>
       </c>
       <c r="F55" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3269,10 +3679,10 @@
         <v>Regional</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J55" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K55">
         <v>1</v>
@@ -3286,22 +3696,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>1787471970177-kr1vda</v>
+        <v>1789045150461-levi</v>
       </c>
       <c r="B56">
-        <v>1787471970177</v>
+        <v>1789045150461</v>
       </c>
       <c r="C56" t="str">
-        <v>kr1vda</v>
+        <v>levi</v>
       </c>
       <c r="D56" t="str">
-        <v>Vox Eminor</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E56" t="str">
         <v>EVENT</v>
       </c>
       <c r="F56" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3310,10 +3720,10 @@
         <v>Regional</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J56" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -3327,22 +3737,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>1787471959675-jambo</v>
+        <v>1789045150461-urban0</v>
       </c>
       <c r="B57">
-        <v>1787471959675</v>
+        <v>1789045150461</v>
       </c>
       <c r="C57" t="str">
-        <v>jambo</v>
+        <v>urban0</v>
       </c>
       <c r="D57" t="str">
-        <v>Fnatic</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E57" t="str">
         <v>EVENT</v>
       </c>
       <c r="F57" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -3351,10 +3761,10 @@
         <v>Regional</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J57" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -3368,22 +3778,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1787471959675-MATYS</v>
+        <v>1789045150461-t9rnay</v>
       </c>
       <c r="B58">
-        <v>1787471959675</v>
+        <v>1789045150461</v>
       </c>
       <c r="C58" t="str">
-        <v>MATYS</v>
+        <v>t9rnay</v>
       </c>
       <c r="D58" t="str">
-        <v>Fnatic</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E58" t="str">
         <v>EVENT</v>
       </c>
       <c r="F58" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3392,10 +3802,10 @@
         <v>Regional</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J58" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K58">
         <v>1</v>
@@ -3409,22 +3819,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1787471959675-fear</v>
+        <v>1789045150461-JOTA</v>
       </c>
       <c r="B59">
-        <v>1787471959675</v>
+        <v>1789045150461</v>
       </c>
       <c r="C59" t="str">
-        <v>fear</v>
+        <v>JOTA</v>
       </c>
       <c r="D59" t="str">
-        <v>Fnatic</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E59" t="str">
         <v>EVENT</v>
       </c>
       <c r="F59" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -3433,10 +3843,10 @@
         <v>Regional</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J59" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -3450,22 +3860,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1787471959675-blameF</v>
+        <v>1789045150461-shz</v>
       </c>
       <c r="B60">
-        <v>1787471959675</v>
+        <v>1789045150461</v>
       </c>
       <c r="C60" t="str">
-        <v>blameF</v>
+        <v>shz</v>
       </c>
       <c r="D60" t="str">
-        <v>Fnatic</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E60" t="str">
         <v>EVENT</v>
       </c>
       <c r="F60" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3474,10 +3884,10 @@
         <v>Regional</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J60" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K60">
         <v>1</v>
@@ -3491,22 +3901,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1787471959675-KRIMZ</v>
+        <v>1789045118610-huncho</v>
       </c>
       <c r="B61">
-        <v>1787471959675</v>
+        <v>1789045118610</v>
       </c>
       <c r="C61" t="str">
-        <v>KRIMZ</v>
+        <v>huncho</v>
       </c>
       <c r="D61" t="str">
-        <v>Fnatic</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E61" t="str">
         <v>EVENT</v>
       </c>
       <c r="F61" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3515,10 +3925,10 @@
         <v>Regional</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J61" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K61">
         <v>1</v>
@@ -3532,16 +3942,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>1784854079769-Benkai</v>
+        <v>1789045118610-Crisp</v>
       </c>
       <c r="B62">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C62" t="str">
-        <v>Benkai</v>
+        <v>Crisp</v>
       </c>
       <c r="D62" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E62" t="str">
         <v>EVENT</v>
@@ -3556,10 +3966,10 @@
         <v>Regional</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J62" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -3573,16 +3983,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>1784854079769-dea</v>
+        <v>1789045118610-FxRE</v>
       </c>
       <c r="B63">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C63" t="str">
-        <v>dea</v>
+        <v>FxRE</v>
       </c>
       <c r="D63" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E63" t="str">
         <v>EVENT</v>
@@ -3597,10 +4007,10 @@
         <v>Regional</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J63" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -3614,16 +4024,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>1784854079769-shane</v>
+        <v>1789045118610-Panic</v>
       </c>
       <c r="B64">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C64" t="str">
-        <v>shane</v>
+        <v>Panic</v>
       </c>
       <c r="D64" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E64" t="str">
         <v>EVENT</v>
@@ -3638,10 +4048,10 @@
         <v>Regional</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J64" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -3655,16 +4065,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>1784854079769-nosraC</v>
+        <v>1789045118610-REKMEISTER</v>
       </c>
       <c r="B65">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C65" t="str">
-        <v>nosraC</v>
+        <v>REKMEISTER</v>
       </c>
       <c r="D65" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E65" t="str">
         <v>EVENT</v>
@@ -3679,10 +4089,10 @@
         <v>Regional</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J65" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K65">
         <v>1</v>
@@ -3696,13 +4106,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>1784854079769-MarKE</v>
+        <v>1784854079769-Benkai</v>
       </c>
       <c r="B66">
         <v>1784854079769</v>
       </c>
       <c r="C66" t="str">
-        <v>MarKE</v>
+        <v>Benkai</v>
       </c>
       <c r="D66" t="str">
         <v>Entropiq</v>
@@ -3720,7 +4130,7 @@
         <v>Regional</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J66" t="str">
         <v>Third</v>
@@ -3737,16 +4147,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>1784854026526-ivz</v>
+        <v>1784854079769-dea</v>
       </c>
       <c r="B67">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C67" t="str">
-        <v>ivz</v>
+        <v>dea</v>
       </c>
       <c r="D67" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E67" t="str">
         <v>EVENT</v>
@@ -3761,10 +4171,10 @@
         <v>Regional</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J67" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K67">
         <v>1</v>
@@ -3778,16 +4188,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>1784854026526-abizz</v>
+        <v>1784854079769-shane</v>
       </c>
       <c r="B68">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C68" t="str">
-        <v>abizz</v>
+        <v>shane</v>
       </c>
       <c r="D68" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E68" t="str">
         <v>EVENT</v>
@@ -3802,10 +4212,10 @@
         <v>Regional</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J68" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -3819,16 +4229,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>1784854026526-nacho</v>
+        <v>1784854079769-nosraC</v>
       </c>
       <c r="B69">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C69" t="str">
-        <v>nacho</v>
+        <v>nosraC</v>
       </c>
       <c r="D69" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E69" t="str">
         <v>EVENT</v>
@@ -3843,10 +4253,10 @@
         <v>Regional</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J69" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K69">
         <v>1</v>
@@ -3860,16 +4270,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>1784854026526-BK1</v>
+        <v>1784854079769-MarKE</v>
       </c>
       <c r="B70">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C70" t="str">
-        <v>BK1</v>
+        <v>MarKE</v>
       </c>
       <c r="D70" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E70" t="str">
         <v>EVENT</v>
@@ -3884,10 +4294,10 @@
         <v>Regional</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J70" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -3901,13 +4311,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>1784854026526-next</v>
+        <v>1784854026526-ivz</v>
       </c>
       <c r="B71">
         <v>1784854026526</v>
       </c>
       <c r="C71" t="str">
-        <v>next</v>
+        <v>ivz</v>
       </c>
       <c r="D71" t="str">
         <v>AMKAL</v>
@@ -3925,7 +4335,7 @@
         <v>Regional</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J71" t="str">
         <v>Second</v>
@@ -3942,16 +4352,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1784854026526-abizz</v>
       </c>
       <c r="B72">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C72" t="str">
-        <v>molodoy</v>
+        <v>abizz</v>
       </c>
       <c r="D72" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E72" t="str">
         <v>EVENT</v>
@@ -3966,10 +4376,10 @@
         <v>Regional</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J72" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K72">
         <v>1</v>
@@ -3983,16 +4393,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1784854026526-nacho</v>
       </c>
       <c r="B73">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C73" t="str">
-        <v>KSCERATO</v>
+        <v>nacho</v>
       </c>
       <c r="D73" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E73" t="str">
         <v>EVENT</v>
@@ -4007,10 +4417,10 @@
         <v>Regional</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J73" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -4024,16 +4434,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1784854026526-BK1</v>
       </c>
       <c r="B74">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C74" t="str">
-        <v>YEKINDAR</v>
+        <v>BK1</v>
       </c>
       <c r="D74" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E74" t="str">
         <v>EVENT</v>
@@ -4048,10 +4458,10 @@
         <v>Regional</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J74" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -4065,16 +4475,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1784854026526-next</v>
       </c>
       <c r="B75">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C75" t="str">
-        <v>yuurih</v>
+        <v>next</v>
       </c>
       <c r="D75" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E75" t="str">
         <v>EVENT</v>
@@ -4089,10 +4499,10 @@
         <v>Regional</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J75" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K75">
         <v>1</v>
@@ -4106,13 +4516,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1784848026994-molodoy</v>
       </c>
       <c r="B76">
         <v>1784848026994</v>
       </c>
       <c r="C76" t="str">
-        <v>FalleN</v>
+        <v>molodoy</v>
       </c>
       <c r="D76" t="str">
         <v>FURIA</v>
@@ -4130,7 +4540,7 @@
         <v>Regional</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J76" t="str">
         <v>Winner</v>
@@ -4146,20 +4556,20 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
-        <v>1784847962039</v>
-      </c>
-      <c r="B77" t="str">
-        <v/>
+      <c r="A77" t="str">
+        <v>1784848026994-KSCERATO</v>
+      </c>
+      <c r="B77">
+        <v>1784848026994</v>
       </c>
       <c r="C77" t="str">
-        <v>abizz</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D77" t="str">
-        <v>AMKAL</v>
+        <v>FURIA</v>
       </c>
       <c r="E77" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F77" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -4171,10 +4581,10 @@
         <v>Regional</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J77" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -4187,20 +4597,20 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
-        <v>1784847955956</v>
-      </c>
-      <c r="B78" t="str">
-        <v/>
+      <c r="A78" t="str">
+        <v>1784848026994-YEKINDAR</v>
+      </c>
+      <c r="B78">
+        <v>1784848026994</v>
       </c>
       <c r="C78" t="str">
-        <v>next</v>
+        <v>YEKINDAR</v>
       </c>
       <c r="D78" t="str">
-        <v>AMKAL</v>
+        <v>FURIA</v>
       </c>
       <c r="E78" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F78" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -4212,10 +4622,10 @@
         <v>Regional</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J78" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K78">
         <v>1</v>
@@ -4228,11 +4638,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
-        <v>1784847948890</v>
-      </c>
-      <c r="B79" t="str">
-        <v/>
+      <c r="A79" t="str">
+        <v>1784848026994-yuurih</v>
+      </c>
+      <c r="B79">
+        <v>1784848026994</v>
       </c>
       <c r="C79" t="str">
         <v>yuurih</v>
@@ -4241,7 +4651,7 @@
         <v>FURIA</v>
       </c>
       <c r="E79" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F79" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -4253,7 +4663,7 @@
         <v>Regional</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J79" t="str">
         <v>Winner</v>
@@ -4269,20 +4679,20 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
-        <v>1784847943609</v>
-      </c>
-      <c r="B80" t="str">
-        <v/>
+      <c r="A80" t="str">
+        <v>1784848026994-FalleN</v>
+      </c>
+      <c r="B80">
+        <v>1784848026994</v>
       </c>
       <c r="C80" t="str">
-        <v>KSCERATO</v>
+        <v>FalleN</v>
       </c>
       <c r="D80" t="str">
         <v>FURIA</v>
       </c>
       <c r="E80" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F80" t="str">
         <v>FiReLEAGUE Buenos Aires 2026</v>
@@ -4294,7 +4704,7 @@
         <v>Regional</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J80" t="str">
         <v>Winner</v>
@@ -4310,35 +4720,35 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
-        <v>1784847935905</v>
-      </c>
-      <c r="B81" t="str">
-        <v/>
+      <c r="A81" t="str">
+        <v>1789044307262-sowalio</v>
+      </c>
+      <c r="B81">
+        <v>1789044307262</v>
       </c>
       <c r="C81" t="str">
-        <v>molodoy</v>
+        <v>sowalio</v>
       </c>
       <c r="D81" t="str">
-        <v>FURIA</v>
+        <v>Nemiga</v>
       </c>
       <c r="E81" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F81" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H81" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -4351,20 +4761,20 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
-        <v>1783531290361</v>
-      </c>
-      <c r="B82" t="str">
-        <v/>
+      <c r="A82" t="str">
+        <v>1789044307262-khaN</v>
+      </c>
+      <c r="B82">
+        <v>1789044307262</v>
       </c>
       <c r="C82" t="str">
-        <v>m0NESY</v>
+        <v>khaN</v>
       </c>
       <c r="D82" t="str">
-        <v>Falcons</v>
+        <v>Nemiga</v>
       </c>
       <c r="E82" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F82" t="str">
         <v>DreamHack Winter 2026</v>
@@ -4379,7 +4789,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -4392,20 +4802,20 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <v>1783531284605</v>
-      </c>
-      <c r="B83" t="str">
-        <v/>
+      <c r="A83" t="str">
+        <v>1789044307262-riskyb0b</v>
+      </c>
+      <c r="B83">
+        <v>1789044307262</v>
       </c>
       <c r="C83" t="str">
-        <v>ropz</v>
+        <v>riskyb0b</v>
       </c>
       <c r="D83" t="str">
-        <v>Vitality</v>
+        <v>Nemiga</v>
       </c>
       <c r="E83" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F83" t="str">
         <v>DreamHack Winter 2026</v>
@@ -4420,7 +4830,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K83">
         <v>1</v>
@@ -4433,20 +4843,20 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
-        <v>1783531278450</v>
-      </c>
-      <c r="B84" t="str">
-        <v/>
+      <c r="A84" t="str">
+        <v>1789044307262-1eeR</v>
+      </c>
+      <c r="B84">
+        <v>1789044307262</v>
       </c>
       <c r="C84" t="str">
-        <v>ZywOo</v>
+        <v>1eeR</v>
       </c>
       <c r="D84" t="str">
-        <v>Vitality</v>
+        <v>Nemiga</v>
       </c>
       <c r="E84" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F84" t="str">
         <v>DreamHack Winter 2026</v>
@@ -4461,7 +4871,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K84">
         <v>1</v>
@@ -4474,20 +4884,20 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
-        <v>1783531271104</v>
-      </c>
-      <c r="B85" t="str">
-        <v/>
+      <c r="A85" t="str">
+        <v>1789044307262-Xant3r</v>
+      </c>
+      <c r="B85">
+        <v>1789044307262</v>
       </c>
       <c r="C85" t="str">
-        <v>heroghoxxt</v>
+        <v>Xant3r</v>
       </c>
       <c r="D85" t="str">
-        <v>Iluminar</v>
+        <v>Nemiga</v>
       </c>
       <c r="E85" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F85" t="str">
         <v>DreamHack Winter 2026</v>
@@ -4502,7 +4912,7 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K85">
         <v>1</v>
@@ -4515,20 +4925,20 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
-        <v>1783531262507</v>
-      </c>
-      <c r="B86" t="str">
-        <v/>
+      <c r="A86" t="str">
+        <v>1789044244253-w0nderful</v>
+      </c>
+      <c r="B86">
+        <v>1789044244253</v>
       </c>
       <c r="C86" t="str">
-        <v>kilzys</v>
+        <v>w0nderful</v>
       </c>
       <c r="D86" t="str">
-        <v>Iluminar</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E86" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F86" t="str">
         <v>DreamHack Winter 2026</v>
@@ -4543,21 +4953,2030 @@
         <v/>
       </c>
       <c r="J86" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>1789044244253-makazze</v>
+      </c>
+      <c r="B87">
+        <v>1789044244253</v>
+      </c>
+      <c r="C87" t="str">
+        <v>makazze</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Natus Vincere</v>
+      </c>
+      <c r="E87" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F87" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>1789044244253-b1t</v>
+      </c>
+      <c r="B88">
+        <v>1789044244253</v>
+      </c>
+      <c r="C88" t="str">
+        <v>b1t</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Natus Vincere</v>
+      </c>
+      <c r="E88" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F88" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>1789044244253-iM</v>
+      </c>
+      <c r="B89">
+        <v>1789044244253</v>
+      </c>
+      <c r="C89" t="str">
+        <v>iM</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Natus Vincere</v>
+      </c>
+      <c r="E89" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F89" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G89">
+        <v>5</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>1789044244253-Aleksib</v>
+      </c>
+      <c r="B90">
+        <v>1789044244253</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Aleksib</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Natus Vincere</v>
+      </c>
+      <c r="E90" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F90" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G90">
+        <v>5</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>1789044197304-Dytor</v>
+      </c>
+      <c r="B91">
+        <v>1789044197304</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Dytor</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E91" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F91" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G91">
+        <v>5</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>1789044197304-nbqq</v>
+      </c>
+      <c r="B92">
+        <v>1789044197304</v>
+      </c>
+      <c r="C92" t="str">
+        <v>nbqq</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E92" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F92" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>1789044197304-forsyy</v>
+      </c>
+      <c r="B93">
+        <v>1789044197304</v>
+      </c>
+      <c r="C93" t="str">
+        <v>forsyy</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E93" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F93" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G93">
+        <v>5</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>1789044197304-ROGA</v>
+      </c>
+      <c r="B94">
+        <v>1789044197304</v>
+      </c>
+      <c r="C94" t="str">
+        <v>ROGA</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E94" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F94" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G94">
+        <v>5</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>1789044197304-DANK1NG</v>
+      </c>
+      <c r="B95">
+        <v>1789044197304</v>
+      </c>
+      <c r="C95" t="str">
+        <v>DANK1NG</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E95" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F95" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G95">
+        <v>5</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>1789044064380-910</v>
+      </c>
+      <c r="B96">
+        <v>1789044064380</v>
+      </c>
+      <c r="C96" t="str">
+        <v>910</v>
+      </c>
+      <c r="D96" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E96" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F96" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G96">
+        <v>5</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>1789044064380-mzinho</v>
+      </c>
+      <c r="B97">
+        <v>1789044064380</v>
+      </c>
+      <c r="C97" t="str">
+        <v>mzinho</v>
+      </c>
+      <c r="D97" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E97" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F97" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>1789044064380-Senzu</v>
+      </c>
+      <c r="B98">
+        <v>1789044064380</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Senzu</v>
+      </c>
+      <c r="D98" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E98" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F98" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>1789044064380-Techno</v>
+      </c>
+      <c r="B99">
+        <v>1789044064380</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Techno</v>
+      </c>
+      <c r="D99" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E99" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F99" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G99">
+        <v>5</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>1789044064380-bLitz</v>
+      </c>
+      <c r="B100">
+        <v>1789044064380</v>
+      </c>
+      <c r="C100" t="str">
+        <v>bLitz</v>
+      </c>
+      <c r="D100" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E100" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F100" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G100">
+        <v>5</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>1789043946191-ultimate</v>
+      </c>
+      <c r="B101">
+        <v>1789043946191</v>
+      </c>
+      <c r="C101" t="str">
+        <v>ultimate</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E101" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F101" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G101">
+        <v>5</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>1789043946191-siuhy</v>
+      </c>
+      <c r="B102">
+        <v>1789043946191</v>
+      </c>
+      <c r="C102" t="str">
+        <v>siuhy</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E102" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F102" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G102">
+        <v>5</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>1789043946191-EliGE</v>
+      </c>
+      <c r="B103">
+        <v>1789043946191</v>
+      </c>
+      <c r="C103" t="str">
+        <v>EliGE</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E103" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F103" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G103">
+        <v>5</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>1789043946191-NertZ</v>
+      </c>
+      <c r="B104">
+        <v>1789043946191</v>
+      </c>
+      <c r="C104" t="str">
+        <v>NertZ</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E104" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F104" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G104">
+        <v>5</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>1789043946191-NAF</v>
+      </c>
+      <c r="B105">
+        <v>1789043946191</v>
+      </c>
+      <c r="C105" t="str">
+        <v>NAF</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E105" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F105" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G105">
+        <v>5</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>1783531237020-mezii</v>
+      </c>
+      <c r="B106">
+        <v>1783531237020</v>
+      </c>
+      <c r="C106" t="str">
+        <v>mezii</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E106" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F106" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G106">
+        <v>5</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>1783531237020-flameZ</v>
+      </c>
+      <c r="B107">
+        <v>1783531237020</v>
+      </c>
+      <c r="C107" t="str">
+        <v>flameZ</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E107" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F107" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G107">
+        <v>5</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>1783531237020-ropz</v>
+      </c>
+      <c r="B108">
+        <v>1783531237020</v>
+      </c>
+      <c r="C108" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E108" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F108" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G108">
+        <v>5</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>1783531237020-apEX</v>
+      </c>
+      <c r="B109">
+        <v>1783531237020</v>
+      </c>
+      <c r="C109" t="str">
+        <v>apEX</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E109" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F109" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G109">
+        <v>5</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>1783531237020-ZywOo</v>
+      </c>
+      <c r="B110">
+        <v>1783531237020</v>
+      </c>
+      <c r="C110" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E110" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F110" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G110">
+        <v>5</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>1783531248336-kyousuke</v>
+      </c>
+      <c r="B111">
+        <v>1783531248336</v>
+      </c>
+      <c r="C111" t="str">
+        <v>kyousuke</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E111" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F111" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G111">
+        <v>5</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>1783531248336-kyxsan</v>
+      </c>
+      <c r="B112">
+        <v>1783531248336</v>
+      </c>
+      <c r="C112" t="str">
+        <v>kyxsan</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E112" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F112" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G112">
+        <v>5</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>1783531248336-NiKo</v>
+      </c>
+      <c r="B113">
+        <v>1783531248336</v>
+      </c>
+      <c r="C113" t="str">
+        <v>NiKo</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E113" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F113" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G113">
+        <v>5</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>1783531248336-TeSeS</v>
+      </c>
+      <c r="B114">
+        <v>1783531248336</v>
+      </c>
+      <c r="C114" t="str">
+        <v>TeSeS</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E114" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F114" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G114">
+        <v>5</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>1783531248336-m0NESY</v>
+      </c>
+      <c r="B115">
+        <v>1783531248336</v>
+      </c>
+      <c r="C115" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E115" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F115" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G115">
+        <v>5</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>1789043725277-heroghoxxt</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E116" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F116" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G116">
+        <v>5</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
         <v>Winner</v>
       </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86" t="str">
-        <v/>
-      </c>
-      <c r="M86" t="str">
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>1789043725277-kilzys</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E117" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F117" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G117">
+        <v>5</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B118">
+        <v>1783531219494</v>
+      </c>
+      <c r="C118" t="str">
+        <v>history</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E118" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F118" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G118">
+        <v>5</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B119">
+        <v>1783531219494</v>
+      </c>
+      <c r="C119" t="str">
+        <v>SpavaQu</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E119" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F119" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G119">
+        <v>5</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B120">
+        <v>1783531219494</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Pelle</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E120" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F120" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G120">
+        <v>5</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>1787472254648</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v>REZ</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Astana Dragons</v>
+      </c>
+      <c r="E121" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>1787472247600</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v>kr1vda</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Vox Eminor</v>
+      </c>
+      <c r="E122" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>1787472243903</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v>fear</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E123" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>1787472232104</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v>KRIMZ</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E124" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>1787472226864</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v>blameF</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E125" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>1784847962039</v>
+      </c>
+      <c r="B126" t="str">
+        <v/>
+      </c>
+      <c r="C126" t="str">
+        <v>abizz</v>
+      </c>
+      <c r="D126" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E126" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F126" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>1784847955956</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v>next</v>
+      </c>
+      <c r="D127" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E127" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F127" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>1784847948890</v>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v>yuurih</v>
+      </c>
+      <c r="D128" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E128" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F128" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>1784847943609</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D129" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E129" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F129" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1784847935905</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D130" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E130" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F130" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1783531290361</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E131" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F131" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G131">
+        <v>5</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1783531284605</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E132" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F132" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G132">
+        <v>5</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1783531278450</v>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E133" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F133" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G133">
+        <v>5</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1783531271104</v>
+      </c>
+      <c r="B134" t="str">
+        <v/>
+      </c>
+      <c r="C134" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E134" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F134" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G134">
+        <v>5</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1783531262507</v>
+      </c>
+      <c r="B135" t="str">
+        <v/>
+      </c>
+      <c r="C135" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E135" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F135" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G135">
+        <v>5</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M135"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -6385,7 +6385,7 @@
         <v>Regional</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J121" t="str">
         <v>Winner</v>
@@ -6426,7 +6426,7 @@
         <v>Regional</v>
       </c>
       <c r="I122" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J122" t="str">
         <v>Winner</v>
@@ -6467,7 +6467,7 @@
         <v>Regional</v>
       </c>
       <c r="I123" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J123" t="str">
         <v>Winner</v>
@@ -6508,7 +6508,7 @@
         <v>Regional</v>
       </c>
       <c r="I124" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J124" t="str">
         <v>Winner</v>
@@ -6549,7 +6549,7 @@
         <v>Regional</v>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J125" t="str">
         <v>Winner</v>
@@ -6590,7 +6590,7 @@
         <v>Regional</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J126" t="str">
         <v>Second</v>
@@ -6631,7 +6631,7 @@
         <v>Regional</v>
       </c>
       <c r="I127" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J127" t="str">
         <v>Second</v>
@@ -6672,7 +6672,7 @@
         <v>Regional</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J128" t="str">
         <v>Winner</v>
@@ -6713,7 +6713,7 @@
         <v>Regional</v>
       </c>
       <c r="I129" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J129" t="str">
         <v>Winner</v>
@@ -6754,7 +6754,7 @@
         <v>Regional</v>
       </c>
       <c r="I130" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J130" t="str">
         <v>Winner</v>
